--- a/exports/Eliquis_Launch_Forecast_v2.xlsx
+++ b/exports/Eliquis_Launch_Forecast_v2.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="420">
   <si>
     <t>Eliquis (Apixaban) - Launch Forecast Modell</t>
   </si>
@@ -141,37 +141,52 @@
     <t>JA oder NEIN - Eigenes Generikum unter Zweitmarke?</t>
   </si>
   <si>
-    <t>AG Anteil am Generika-Segment</t>
-  </si>
-  <si>
-    <t>Anteil der Generika-Verordnungen fuer AG</t>
-  </si>
-  <si>
-    <t>AG Preis-Discount vs. Originator</t>
-  </si>
-  <si>
-    <t>Preisabschlag des AG</t>
+    <t>AG Anteil am Generika-Segment (initial)</t>
+  </si>
+  <si>
+    <t>Initialer Anteil der Generika-Verordnungen fuer AG</t>
+  </si>
+  <si>
+    <t>AG Anteil-Erosion Speed</t>
+  </si>
+  <si>
+    <t>0=statisch, 1=moderate Erosion, 2=schnelle Erosion</t>
+  </si>
+  <si>
+    <t>AG Preis-Discount vs. Originator (initial)</t>
+  </si>
+  <si>
+    <t>Initialer Preisabschlag des AG</t>
+  </si>
+  <si>
+    <t>AG Discount-Zunahme Speed</t>
+  </si>
+  <si>
+    <t>0=statisch, 1=moderater Preisverfall, 2=schneller Preisverfall</t>
   </si>
   <si>
     <t>3. GENERIKA-PARAMETER (Market Opportunity)</t>
   </si>
   <si>
-    <t>Firmenname</t>
-  </si>
-  <si>
-    <t>Mein Unternehmen</t>
-  </si>
-  <si>
-    <t>Name des Generika-Anbieters</t>
-  </si>
-  <si>
-    <t>Produktname</t>
-  </si>
-  <si>
-    <t>Apixaban [Firma]</t>
-  </si>
-  <si>
-    <t>Name des Generikums</t>
+    <t>Markt-Kaskade: NOAK -&gt; Apixaban (42%) -&gt; Generika-Segment (55%) -&gt; Mein Anteil (20%)</t>
+  </si>
+  <si>
+    <t>Apixaban-Marktanteil am NOAK-Markt</t>
+  </si>
+  <si>
+    <t>Anteil von Apixaban (Eliquis) am NOAK-Gesamtmarkt</t>
+  </si>
+  <si>
+    <t>Generika-Segment Peak-Anteil</t>
+  </si>
+  <si>
+    <t>Anteil der Apixaban-Verordnungen, die generisch werden</t>
+  </si>
+  <si>
+    <t>Monate bis Generika-Segment Peak</t>
+  </si>
+  <si>
+    <t>Monate nach LOE bis Generika-Segment seinen Peak erreicht</t>
   </si>
   <si>
     <t>Launch-Zeitpunkt (Monate nach LOE)</t>
@@ -186,16 +201,16 @@
     <t>Preisabschlag zum Originator-Preis</t>
   </si>
   <si>
-    <t>Ziel Peak-Marktanteil (Gesamtmarkt)</t>
-  </si>
-  <si>
-    <t>Angestrebter Anteil am gesamten NOAK-Markt</t>
+    <t>Mein Anteil am Generika-Segment</t>
+  </si>
+  <si>
+    <t>Mein Anteil an allen Apixaban-Generika (nicht am NOAK-Gesamtmarkt)</t>
   </si>
   <si>
     <t>Monate bis Peak Share</t>
   </si>
   <si>
-    <t>Monate bis Ziel-Marktanteil erreicht</t>
+    <t>Monate bis mein Anteil am Generika-Segment den Peak erreicht</t>
   </si>
   <si>
     <t>4. AUT-IDEM / SUBSTITUTION</t>
@@ -228,13 +243,7 @@
     <t>Peak Aut-idem-Quote</t>
   </si>
   <si>
-    <t>Max. Anteil der Rx, die substituiert werden</t>
-  </si>
-  <si>
-    <t>Mein Anteil an Aut-idem-Substitutionen</t>
-  </si>
-  <si>
-    <t>Welchen Anteil der Substitutionen bekomme ich?</t>
+    <t>Max. Anteil der Rx, die substituiert werden (Nicht-Tender-Rest)</t>
   </si>
   <si>
     <t>Aut-idem Wirkungskette</t>
@@ -258,7 +267,10 @@
     <t>6. Patient erhaelt Generikum, es sei denn Arzt hat es ausgeschlossen</t>
   </si>
   <si>
-    <t>5. RABATTVERTRAEGE &amp; TENDER</t>
+    <t>5. MEINE RABATTVERTRAEGE</t>
+  </si>
+  <si>
+    <t>Deterministisches Modell: Pro Kasse gewonnen/verloren. Risiko als Szenario-Band (Bear/Base/Bull).</t>
   </si>
   <si>
     <t>Rabattvertraege anstreben?</t>
@@ -273,13 +285,13 @@
     <t>Bis erste Ausschreibung gewonnen</t>
   </si>
   <si>
-    <t>Tender-Vertragslaufzeit (Monate)</t>
-  </si>
-  <si>
-    <t>Typische Laufzeit Rabattvertrag</t>
-  </si>
-  <si>
-    <t>Ziel-Krankenkassen fuer Rabattvertraege</t>
+    <t>Mein Anteil bei Mehrfachvergabe</t>
+  </si>
+  <si>
+    <t>z.B. 50% bei 2 Hauptpartnern pro Kasse</t>
+  </si>
+  <si>
+    <t>Kassen - Rabattvertrag gewonnen/verloren (Base Case)</t>
   </si>
   <si>
     <t>Krankenkasse</t>
@@ -293,17 +305,17 @@
 GKV</t>
   </si>
   <si>
-    <t>Gewinn-
-wahrsch.</t>
-  </si>
-  <si>
-    <t>Prioritaet</t>
+    <t>Gewonnen?
+(Base)</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>TK (Techniker)</t>
   </si>
   <si>
-    <t>Hoch</t>
+    <t>Ziel</t>
   </si>
   <si>
     <t>BARMER</t>
@@ -315,49 +327,37 @@
     <t>AOK Bayern</t>
   </si>
   <si>
-    <t>Mittel</t>
+    <t>Optional</t>
   </si>
   <si>
     <t>AOK Baden-Wuerttemberg</t>
   </si>
   <si>
-    <t>AOK Nordwest</t>
-  </si>
-  <si>
-    <t>AOK Rheinland/Hamburg</t>
-  </si>
-  <si>
-    <t>IKK classic</t>
+    <t>Restl. Kassen</t>
   </si>
   <si>
     <t>Nachrangig</t>
   </si>
   <si>
-    <t>KKH</t>
-  </si>
-  <si>
-    <t>hkk</t>
-  </si>
-  <si>
     <t>Rabattvertrag-Mechanik</t>
   </si>
   <si>
-    <t>1. Krankenkasse schreibt Wirkstoff aus (Open-House oder Exklusiv)</t>
+    <t>1. Krankenkasse schreibt Wirkstoff aus (Open-House oder Mehrfachvergabe)</t>
   </si>
   <si>
     <t>2. Generika-Anbieter geben Angebot ab (Preis pro DDD/Packung)</t>
   </si>
   <si>
-    <t>3. Zuschlag: Guenstigster Anbieter gewinnt -&gt; Exklusivvertrag</t>
-  </si>
-  <si>
-    <t>4. Apotheke MUSS Produkt des Vertragpartners abgeben (Par.130a SGB V)</t>
-  </si>
-  <si>
-    <t>5. Volumen-Garantie: Alle Versicherten der Kasse = gesichertes Volumen</t>
-  </si>
-  <si>
-    <t>6. Laufzeit typisch 24 Monate, danach Neuausschreibung</t>
+    <t>3. Zuschlag: Mehrere Anbieter erhalten Vertrag (Versorgungssicherheit)</t>
+  </si>
+  <si>
+    <t>4. Apotheke MUSS Produkt eines Vertragspartners abgeben (Par.130a SGB V)</t>
+  </si>
+  <si>
+    <t>5. Aut-idem-Ausschluss durch Arzt hat Vorrang und verhindert Tender-Substitution</t>
+  </si>
+  <si>
+    <t>6. Modellierung: Deterministisch (gewonnen/verloren) + Szenario-Band fuer Risiko</t>
   </si>
   <si>
     <t>6. KOSTEN &amp; PROFITABILITAET (Generika)</t>
@@ -411,10 +411,7 @@
     <t>Aut-idem Peak-Quote</t>
   </si>
   <si>
-    <t>Mein Peak Share</t>
-  </si>
-  <si>
-    <t>Generika-Segment Peak</t>
+    <t>Generika-Segment Peak Share</t>
   </si>
   <si>
     <t>Mein Preis-Discount</t>
@@ -423,10 +420,16 @@
     <t>Marktwachstum p.a.</t>
   </si>
   <si>
-    <t>Tender-Gewinnquote (Durchschn.)</t>
-  </si>
-  <si>
-    <t>Mein Aut-idem-Anteil</t>
+    <t>Tender</t>
+  </si>
+  <si>
+    <t>Kein Tender</t>
+  </si>
+  <si>
+    <t>User-Auswahl</t>
+  </si>
+  <si>
+    <t>Alle Kassen</t>
   </si>
   <si>
     <t>Wettbewerbslandschaft - NOAK/DOAK Deutschland</t>
@@ -817,7 +820,7 @@
     <t>Break-Even</t>
   </si>
   <si>
-    <t>Monat 2</t>
+    <t>Monat 8</t>
   </si>
   <si>
     <t>Volumen-Dekomposition (5 Jahre)</t>
@@ -827,9 +830,6 @@
   </si>
   <si>
     <t>Aut-idem</t>
-  </si>
-  <si>
-    <t>Tender</t>
   </si>
   <si>
     <t>Organisch
@@ -1049,13 +1049,28 @@
     <t>Strategische Entscheidung des Originators</t>
   </si>
   <si>
-    <t>Peak Marktanteil Generikum</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>Abhaengig von Vertrieb, Tender, Timing</t>
+    <t>Apixaban-Marktanteil</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>Anteil von Apixaban am NOAK-Gesamtmarkt</t>
+  </si>
+  <si>
+    <t>Generika-Segment Peak</t>
+  </si>
+  <si>
+    <t>55%</t>
+  </si>
+  <si>
+    <t>Anteil der Apixaban-Rx, die generisch werden</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Marktanteil unter den Apixaban-Generika</t>
   </si>
   <si>
     <t>Monate bis Peak</t>
@@ -1091,13 +1106,22 @@
     <t>G-BA braucht 3-6 Monate fuer Festbetragsgruppe</t>
   </si>
   <si>
-    <t>Tender-Gewinnwahrsch.</t>
-  </si>
-  <si>
-    <t>20-60%</t>
-  </si>
-  <si>
-    <t>Pro Kasse individuell, abhaengig von Preisaggression</t>
+    <t>Tender pro Kasse</t>
+  </si>
+  <si>
+    <t>Deterministisch</t>
+  </si>
+  <si>
+    <t>Gewonnen/Verloren pro Kasse, Risiko als Szenario-Band</t>
+  </si>
+  <si>
+    <t>Mein Tender-Anteil (Mehrfachvergabe)</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>2 Hauptpartner pro Kasse (Versorgungssicherheit)</t>
   </si>
   <si>
     <t>COGS</t>
@@ -1118,6 +1142,15 @@
     <t>Firmenspezifisch</t>
   </si>
   <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>AG verliert Anteil an unabh. Generika; 0=statisch, 2=schnell</t>
+  </si>
+  <si>
+    <t>AG-Preis naehert sich Generika-Preis an; 0=statisch, 2=schnell</t>
+  </si>
+  <si>
     <t>MATHEMATISCHE MODELLE</t>
   </si>
   <si>
@@ -1160,10 +1193,10 @@
     <t>Tender-Effekt</t>
   </si>
   <si>
-    <t>Erwartungswert: Sum(Kasse_share * Win_prob) * Ramp * Exklusivitaetsfaktor</t>
-  </si>
-  <si>
-    <t>Kein binares Modell; gewichteter Durchschnitt ueber Kassen-Portfolio</t>
+    <t>Deterministisch: Sum(gewonnene Kasse_shares) * Ramp * Aut-idem-Rate * My_Share</t>
+  </si>
+  <si>
+    <t>Binaer pro Kasse (gewonnen/verloren); Risiko als Szenario-Band (Bear/Base/Bull)</t>
   </si>
   <si>
     <t>Preis-Erosion</t>
@@ -1173,6 +1206,24 @@
   </si>
   <si>
     <t>Beobachteter Trend in reifen Generika-Maerkten</t>
+  </si>
+  <si>
+    <t>AG Anteil-Erosion</t>
+  </si>
+  <si>
+    <t>AG_Share(t) = max(2%, Initial * e^(-speed*0.05*t))</t>
+  </si>
+  <si>
+    <t>AG verliert Anteil an unabh. Generika ueber Zeit; Floor bei 2%</t>
+  </si>
+  <si>
+    <t>AG Discount-Zunahme</t>
+  </si>
+  <si>
+    <t>AG_Disc(t) = min(85%, 1 - (1-Init) * e^(-speed*0.03*t))</t>
+  </si>
+  <si>
+    <t>AG-Preis naehert sich Generika-Niveau an; Cap bei 85%</t>
   </si>
   <si>
     <t>LUECKEN (fuer Produktiveinsatz benoetigt)</t>
@@ -1912,181 +1963,181 @@
                   <c:v>164663857.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>143203548.15</c:v>
+                  <c:v>143199535.16</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>125211203.17</c:v>
+                  <c:v>125204000.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>110101876.8</c:v>
+                  <c:v>110105128.96</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>97388180.55</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>86664213.56</c:v>
+                  <c:v>86661507.42</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>77592073.2</c:v>
+                  <c:v>77587084.95999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>70825259.31999999</c:v>
+                  <c:v>70820706.11</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>65276401.95</c:v>
+                  <c:v>65272205.46</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>60733253.1</c:v>
+                  <c:v>60729348.68</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>57019885.72</c:v>
+                  <c:v>57016220.03</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>53990627.25</c:v>
+                  <c:v>53987156.3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>51524848.65</c:v>
+                  <c:v>51521536.22</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>49963204.42</c:v>
+                  <c:v>49959992.39</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>48649273.57</c:v>
+                  <c:v>48646146.01</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>47545335.22</c:v>
+                  <c:v>47542278.63</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>46619579.4</c:v>
+                  <c:v>46616582.32</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>45844940.4</c:v>
+                  <c:v>45841993.12</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>45198474.6</c:v>
+                  <c:v>45195568.88</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>44660816.02</c:v>
+                  <c:v>44657944.87</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>44215320.82</c:v>
+                  <c:v>44212478.31</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>43848067.27</c:v>
+                  <c:v>43845248.37</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>43547155.8</c:v>
+                  <c:v>43544356.24</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>43302553.42</c:v>
+                  <c:v>43299769.59</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>43105782.67</c:v>
+                  <c:v>43103011.49</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>42949532.7</c:v>
+                  <c:v>42946771.56</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>42827659.27</c:v>
+                  <c:v>42824905.97</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>42734951.47</c:v>
+                  <c:v>42732204.13</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>42666976.12</c:v>
+                  <c:v>42664233.15</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>42620077.8</c:v>
+                  <c:v>42617337.84</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>42591067.72</c:v>
+                  <c:v>42588329.63</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>42577146</c:v>
+                  <c:v>42574408.8</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>42576134.92</c:v>
+                  <c:v>42573397.79</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>42586012.35</c:v>
+                  <c:v>42583274.58</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>42605222.77</c:v>
+                  <c:v>42602483.77</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>42632288.47</c:v>
+                  <c:v>42629547.73</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>42666120.6</c:v>
+                  <c:v>42663377.68</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>42705630.3</c:v>
+                  <c:v>42702884.84</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>42750039.82</c:v>
+                  <c:v>42747291.51</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>42798571.42</c:v>
+                  <c:v>42795819.99</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>42850680.67</c:v>
+                  <c:v>42847925.89</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>42905745.37</c:v>
+                  <c:v>42902987.05</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>42963376.65</c:v>
+                  <c:v>42960614.62</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>43023263.4</c:v>
+                  <c:v>43020497.52</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>43084938.97</c:v>
+                  <c:v>43082169.13</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>43148325.6</c:v>
+                  <c:v>43145551.68</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>43213034.4</c:v>
+                  <c:v>43210256.32</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>43278987.6</c:v>
+                  <c:v>43276205.28</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>43345951.87</c:v>
+                  <c:v>43343165.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>43413849.45</c:v>
+                  <c:v>43411058.46</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>43482524.77</c:v>
+                  <c:v>43479729.37</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>43551822.3</c:v>
+                  <c:v>43549022.44</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>43621742.02</c:v>
+                  <c:v>43618937.67</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>43692206.17</c:v>
+                  <c:v>43689397.29</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>43763059.2</c:v>
+                  <c:v>43760245.76</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>43834378.87</c:v>
+                  <c:v>43831560.85</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>43906087.42</c:v>
+                  <c:v>43903264.79</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>43978107.07</c:v>
+                  <c:v>43975279.81</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>44050360.05</c:v>
+                  <c:v>44047528.14</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>44123001.9</c:v>
+                  <c:v>44120165.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3489,181 +3540,181 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21734717.85</c:v>
+                  <c:v>21738730.84</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>61736646.68</c:v>
+                  <c:v>61747861.92</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>117123316.88</c:v>
+                  <c:v>117131279.96</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>185499464.33</c:v>
+                  <c:v>185507427.41</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>264875817.27</c:v>
+                  <c:v>264886486.49</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>353601098.07</c:v>
+                  <c:v>353616755.53</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>449370346.25</c:v>
+                  <c:v>449390556.92</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>550966154.3</c:v>
+                  <c:v>550990561.46</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>657383179.6999999</c:v>
+                  <c:v>657411491.28</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>767792189.9799999</c:v>
+                  <c:v>767824167.25</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>881509533.7299999</c:v>
+                  <c:v>881544981.95</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>997972188.5799999</c:v>
+                  <c:v>998010949.23</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1116276386.16</c:v>
+                  <c:v>1116318358.84</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1236174962.09</c:v>
+                  <c:v>1236220062.33</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1357458472.87</c:v>
+                  <c:v>1357506629.7</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1479949101.97</c:v>
+                  <c:v>1480000255.88</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1603496190.07</c:v>
+                  <c:v>1603550291.26</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1727972112.97</c:v>
+                  <c:v>1728029119.88</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1853268429.44</c:v>
+                  <c:v>1853328307.51</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1979293525.12</c:v>
+                  <c:v>1979356245.7</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2105969615.84</c:v>
+                  <c:v>2106035155.33</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2233230817.04</c:v>
+                  <c:v>2233299156.09</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>2361021277.12</c:v>
+                  <c:v>2361092400</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2489293713.45</c:v>
+                  <c:v>2489367607.51</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2618007971.25</c:v>
+                  <c:v>2618084626.45</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>2747130222.97</c:v>
+                  <c:v>2747209631.48</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2876631760.5</c:v>
+                  <c:v>2876713916.35</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>3006488308.88</c:v>
+                  <c:v>3006573207.7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>3136679340.08</c:v>
+                  <c:v>3136766978.86</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>3267187423.36</c:v>
+                  <c:v>3267277800.23</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>3397997927.86</c:v>
+                  <c:v>3398091041.93</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3529098400.44</c:v>
+                  <c:v>3529194251.64</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>3660478410.09</c:v>
+                  <c:v>3660576999.06</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>3792129172.81</c:v>
+                  <c:v>3792230500.79</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>3924043290.84</c:v>
+                  <c:v>3924147359.56</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>4056214546.74</c:v>
+                  <c:v>4056321358.38</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>4188637628.94</c:v>
+                  <c:v>4188747186.04</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>4321308186.62</c:v>
+                  <c:v>4321420492.03</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>4454222646.7</c:v>
+                  <c:v>4454337703.54</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>4587377797.53</c:v>
+                  <c:v>4587495609.15</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>4720771232.65</c:v>
+                  <c:v>4720891802.599999</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>4854400843</c:v>
+                  <c:v>4854524174.98</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4988264922.1</c:v>
+                  <c:v>4988391019.959999</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>5122362138.63</c:v>
+                  <c:v>5122491006.329999</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>5256691239.03</c:v>
+                  <c:v>5256822880.649999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5391251450.13</c:v>
+                  <c:v>5391385869.829999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>5526041985.03</c:v>
+                  <c:v>5526179187.049999</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>5661062381.65</c:v>
+                  <c:v>5661202370.299999</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>5796312164.2</c:v>
+                  <c:v>5796454943.839999</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>5931791012.42</c:v>
+                  <c:v>5931936587.469999</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>6067498853.12</c:v>
+                  <c:v>6067647228.03</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>6203435521.59</c:v>
+                  <c:v>6203586700.86</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>6339601022.41</c:v>
+                  <c:v>6339755010.57</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>6475995424.21</c:v>
+                  <c:v>6476152225.809999</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>6612618717.83</c:v>
+                  <c:v>6612778337.459999</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>6749471063.4</c:v>
+                  <c:v>6749633505.669999</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>6886552698.83</c:v>
+                  <c:v>6886717968.359999</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>7023863848.28</c:v>
+                  <c:v>7024031949.719998</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>7161404580.38</c:v>
+                  <c:v>7161575518.399999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3964,184 +4015,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>9129</c:v>
+                  <c:v>765</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12527</c:v>
+                  <c:v>1259</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17073</c:v>
+                  <c:v>2051</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23061</c:v>
+                  <c:v>3297</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30786</c:v>
+                  <c:v>5212</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40492</c:v>
+                  <c:v>8074</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>52291</c:v>
+                  <c:v>12200</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>66070</c:v>
+                  <c:v>15443</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>81432</c:v>
+                  <c:v>18387</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>97703</c:v>
+                  <c:v>20372</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>114027</c:v>
+                  <c:v>21034</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>129547</c:v>
+                  <c:v>19620</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>143569</c:v>
+                  <c:v>15702</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>155676</c:v>
+                  <c:v>18723</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>165736</c:v>
+                  <c:v>21704</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>173842</c:v>
+                  <c:v>24552</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>180221</c:v>
+                  <c:v>27200</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>185161</c:v>
+                  <c:v>29609</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>188950</c:v>
+                  <c:v>31764</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>191844</c:v>
+                  <c:v>33663</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>194058</c:v>
+                  <c:v>35318</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>195765</c:v>
+                  <c:v>36747</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>197096</c:v>
+                  <c:v>37973</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>198152</c:v>
+                  <c:v>39020</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>199008</c:v>
+                  <c:v>39910</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>199719</c:v>
+                  <c:v>40666</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>200324</c:v>
+                  <c:v>41307</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>200854</c:v>
+                  <c:v>41851</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>201330</c:v>
+                  <c:v>42314</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>201767</c:v>
+                  <c:v>42709</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>202176</c:v>
+                  <c:v>43048</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>202566</c:v>
+                  <c:v>43339</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>202941</c:v>
+                  <c:v>43593</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>203306</c:v>
+                  <c:v>43814</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>203664</c:v>
+                  <c:v>44009</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>204018</c:v>
+                  <c:v>44182</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>204368</c:v>
+                  <c:v>44338</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>204715</c:v>
+                  <c:v>44479</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>205062</c:v>
+                  <c:v>44609</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>205407</c:v>
+                  <c:v>44728</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>205752</c:v>
+                  <c:v>44840</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>206097</c:v>
+                  <c:v>44945</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>206442</c:v>
+                  <c:v>45045</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>206787</c:v>
+                  <c:v>45141</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>207132</c:v>
+                  <c:v>45233</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>207478</c:v>
+                  <c:v>45322</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>207824</c:v>
+                  <c:v>45409</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>208171</c:v>
+                  <c:v>45493</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>208518</c:v>
+                  <c:v>45577</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>208866</c:v>
+                  <c:v>45659</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>209214</c:v>
+                  <c:v>45740</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>209563</c:v>
+                  <c:v>45821</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>209912</c:v>
+                  <c:v>45900</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>210262</c:v>
+                  <c:v>45980</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>210612</c:v>
+                  <c:v>46059</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>210963</c:v>
+                  <c:v>46137</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>211315</c:v>
+                  <c:v>46216</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>211667</c:v>
+                  <c:v>46294</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>212020</c:v>
+                  <c:v>46372</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>212373</c:v>
+                  <c:v>46450</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4374,163 +4425,163 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>44221</c:v>
+                  <c:v>2206</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>78107</c:v>
+                  <c:v>6128</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100723</c:v>
+                  <c:v>12222</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>112306</c:v>
+                  <c:v>21033</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>114279</c:v>
+                  <c:v>32698</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>121473</c:v>
+                  <c:v>47105</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>121675</c:v>
+                  <c:v>56169</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>121878</c:v>
+                  <c:v>65112</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>122081</c:v>
+                  <c:v>73654</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>122285</c:v>
+                  <c:v>81598</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>122489</c:v>
+                  <c:v>88827</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>122693</c:v>
+                  <c:v>95289</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>122897</c:v>
+                  <c:v>100986</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>123102</c:v>
+                  <c:v>105951</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>123307</c:v>
+                  <c:v>110240</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>123513</c:v>
+                  <c:v>113919</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>123719</c:v>
+                  <c:v>117058</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>123925</c:v>
+                  <c:v>119730</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>124131</c:v>
+                  <c:v>121996</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>124338</c:v>
+                  <c:v>123919</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>124545</c:v>
+                  <c:v>125551</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>124753</c:v>
+                  <c:v>126940</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>124961</c:v>
+                  <c:v>128125</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>125169</c:v>
+                  <c:v>129141</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>125378</c:v>
+                  <c:v>130017</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>125587</c:v>
+                  <c:v>130776</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>125796</c:v>
+                  <c:v>131440</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>126006</c:v>
+                  <c:v>132025</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>126216</c:v>
+                  <c:v>132546</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>126426</c:v>
+                  <c:v>133013</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>126637</c:v>
+                  <c:v>133437</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>126848</c:v>
+                  <c:v>133825</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>127059</c:v>
+                  <c:v>134184</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>127271</c:v>
+                  <c:v>134519</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>127483</c:v>
+                  <c:v>134835</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>127696</c:v>
+                  <c:v>135134</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>127908</c:v>
+                  <c:v>135420</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>128122</c:v>
+                  <c:v>135696</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>128335</c:v>
+                  <c:v>135964</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>128549</c:v>
+                  <c:v>136224</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>128763</c:v>
+                  <c:v>136479</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>128978</c:v>
+                  <c:v>136729</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>129193</c:v>
+                  <c:v>136976</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>129408</c:v>
+                  <c:v>137219</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>129624</c:v>
+                  <c:v>137460</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>129840</c:v>
+                  <c:v>137700</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>130056</c:v>
+                  <c:v>137938</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>130273</c:v>
+                  <c:v>138174</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>130490</c:v>
+                  <c:v>138411</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>130708</c:v>
+                  <c:v>138645</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>130926</c:v>
+                  <c:v>138880</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>131144</c:v>
+                  <c:v>139115</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>131362</c:v>
+                  <c:v>139350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4754,172 +4805,172 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2901</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7632</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14785</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24908</c:v>
+                  <c:v>262</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38374</c:v>
+                  <c:v>933</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>55251</c:v>
+                  <c:v>2303</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>64482</c:v>
+                  <c:v>4059</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>73258</c:v>
+                  <c:v>6466</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>81188</c:v>
+                  <c:v>9551</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>88034</c:v>
+                  <c:v>11389</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>93723</c:v>
+                  <c:v>13202</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>105630</c:v>
+                  <c:v>14934</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>109506</c:v>
+                  <c:v>16545</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>112508</c:v>
+                  <c:v>18011</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>114810</c:v>
+                  <c:v>19321</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>116569</c:v>
+                  <c:v>20476</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>117914</c:v>
+                  <c:v>21483</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>118951</c:v>
+                  <c:v>22352</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>119760</c:v>
+                  <c:v>23098</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>120402</c:v>
+                  <c:v>23735</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>120922</c:v>
+                  <c:v>24276</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>121354</c:v>
+                  <c:v>24736</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>121721</c:v>
+                  <c:v>25126</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>122043</c:v>
+                  <c:v>25457</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>122333</c:v>
+                  <c:v>25739</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>122598</c:v>
+                  <c:v>25979</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>122847</c:v>
+                  <c:v>26185</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>123084</c:v>
+                  <c:v>26362</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>123312</c:v>
+                  <c:v>26516</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>123533</c:v>
+                  <c:v>26651</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>123751</c:v>
+                  <c:v>26770</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>123966</c:v>
+                  <c:v>26875</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>124179</c:v>
+                  <c:v>26970</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>124389</c:v>
+                  <c:v>27056</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>124600</c:v>
+                  <c:v>27134</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>124810</c:v>
+                  <c:v>27207</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>125020</c:v>
+                  <c:v>27275</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>125229</c:v>
+                  <c:v>27339</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>125439</c:v>
+                  <c:v>27400</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>125648</c:v>
+                  <c:v>27458</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>125858</c:v>
+                  <c:v>27514</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>126068</c:v>
+                  <c:v>27568</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>126279</c:v>
+                  <c:v>27621</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>126489</c:v>
+                  <c:v>27673</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>126700</c:v>
+                  <c:v>27723</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>126912</c:v>
+                  <c:v>27773</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>127123</c:v>
+                  <c:v>27823</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>127335</c:v>
+                  <c:v>27872</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>127547</c:v>
+                  <c:v>27920</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>127760</c:v>
+                  <c:v>27968</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>127973</c:v>
+                  <c:v>28016</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>128186</c:v>
+                  <c:v>28064</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>128400</c:v>
+                  <c:v>28112</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>128614</c:v>
+                  <c:v>28160</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>128828</c:v>
+                  <c:v>28207</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>129043</c:v>
+                  <c:v>28255</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5226,184 +5277,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>459416.93</c:v>
+                  <c:v>38502.45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>626982.61</c:v>
+                  <c:v>63012.95</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>849825.65</c:v>
+                  <c:v>102098.78</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1141554.09</c:v>
+                  <c:v>163201.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1658309.95</c:v>
+                  <c:v>256586.76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2355790.11</c:v>
+                  <c:v>395222.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3265125.53</c:v>
+                  <c:v>593896</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6544104.8</c:v>
+                  <c:v>866892.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9525354.779999999</c:v>
+                  <c:v>1224812.24</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12139586</c:v>
+                  <c:v>1669821.45</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13836977.7</c:v>
+                  <c:v>2194675.08</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>14999817.16</c:v>
+                  <c:v>2781071.04</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16283543.13</c:v>
+                  <c:v>3402996.74</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>17084123.75</c:v>
+                  <c:v>4034499.56</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>17725306.43</c:v>
+                  <c:v>4648836.64</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>18554760.25</c:v>
+                  <c:v>5228199.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>18924947.2</c:v>
+                  <c:v>5757003.99</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>19183784.04</c:v>
+                  <c:v>6230170.02</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>19354142.95</c:v>
+                  <c:v>6642452.12</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>19456178.45</c:v>
+                  <c:v>6997688.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>19506542.79</c:v>
+                  <c:v>7297799.68</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>19518523.89</c:v>
+                  <c:v>7545745.84</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>19502181.53</c:v>
+                  <c:v>7750307.1</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>19465098.14</c:v>
+                  <c:v>7913570.13</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>19412886.14</c:v>
+                  <c:v>8044485.84</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>19349678.85</c:v>
+                  <c:v>8144317.08</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19278389</c:v>
+                  <c:v>8221302.88</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19201302.27</c:v>
+                  <c:v>8275579.69</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19120009.82</c:v>
+                  <c:v>8314501.52</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>19035471.33</c:v>
+                  <c:v>8336998.68</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>18948581.28</c:v>
+                  <c:v>8349561.66</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>18859961.33</c:v>
+                  <c:v>8352206.76</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>18769885.44</c:v>
+                  <c:v>8344762.9</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>18678662.23</c:v>
+                  <c:v>8332619.35</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>18586633.63</c:v>
+                  <c:v>8312935.96</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>18493888.5</c:v>
+                  <c:v>8290714.16</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>18400473.04</c:v>
+                  <c:v>8262741.24</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>18306432.36</c:v>
+                  <c:v>8233725.24</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>18212009.94</c:v>
+                  <c:v>8200107.52</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>18117046.48</c:v>
+                  <c:v>8166434.78</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>18021701.84</c:v>
+                  <c:v>8131047.9</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>17925897.03</c:v>
+                  <c:v>8092139.33</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>17829749.29</c:v>
+                  <c:v>8054065.2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>17733102.87</c:v>
+                  <c:v>8012891.88</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>17636150.66</c:v>
+                  <c:v>7972944.75</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>17538776.27</c:v>
+                  <c:v>7930186.38</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>17441055.1</c:v>
+                  <c:v>7888875.8</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>17342910.64</c:v>
+                  <c:v>7844915.9</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>17244417.2</c:v>
+                  <c:v>7802577.35</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>17145573.14</c:v>
+                  <c:v>7757742.96</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>17046267</c:v>
+                  <c:v>7714621.2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>17074705.2</c:v>
+                  <c:v>7728199.8</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>17103143.4</c:v>
+                  <c:v>7741632</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>17131654.8</c:v>
+                  <c:v>7755027.6</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>17160202.8</c:v>
+                  <c:v>7768313.4</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>17188787.4</c:v>
+                  <c:v>7781599.2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17217481.8</c:v>
+                  <c:v>7794811.8</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17246176.2</c:v>
+                  <c:v>7808024.4</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17274907.2</c:v>
+                  <c:v>7821200.4</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17303674.8</c:v>
+                  <c:v>7834413</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5625,184 +5676,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>-355437.31</c:v>
+                  <c:v>-671123.16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-85200.35000000001</c:v>
+                  <c:v>-823863.45</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>352168.89</c:v>
+                  <c:v>-947289.36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1008334.46</c:v>
+                  <c:v>-1024888.24</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2052066.92</c:v>
+                  <c:v>-1032448.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3618909.5</c:v>
+                  <c:v>-936031.45</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5867753.65</c:v>
+                  <c:v>-690609.45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10575832.25</c:v>
+                  <c:v>-240440.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17519848.33</c:v>
+                  <c:v>478169.03</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>26424537.83</c:v>
+                  <c:v>1530535.12</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>36602271.1</c:v>
+                  <c:v>2976541.43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>47652133.97</c:v>
+                  <c:v>4862344.71</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>59664791.32</c:v>
+                  <c:v>7214592.27</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>72277884.13</c:v>
+                  <c:v>10040466.94</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>85371863.95999999</c:v>
+                  <c:v>13327094.42</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99087934.15000001</c:v>
+                  <c:v>17048243.97</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>113081644.54</c:v>
+                  <c:v>21165996.96</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>127269482.57</c:v>
+                  <c:v>25638624.48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>141585089.79</c:v>
+                  <c:v>30420463.57</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>155977223.62</c:v>
+                  <c:v>35468730.13</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>170407130.72</c:v>
+                  <c:v>40742079.89</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>184846023.63</c:v>
+                  <c:v>46201389.27</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>199272659.78</c:v>
+                  <c:v>51814119.59</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>213671483.39</c:v>
+                  <c:v>57549297.19</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>228031147.99</c:v>
+                  <c:v>63382661.57</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>242343407.13</c:v>
+                  <c:v>69290899.38</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>256602198.88</c:v>
+                  <c:v>75256876.54000001</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>270803175.58</c:v>
+                  <c:v>81263561.31</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>284943182.95</c:v>
+                  <c:v>87299437.45</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>299019786.44</c:v>
+                  <c:v>93352186.45999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>313031222.4</c:v>
+                  <c:v>99414357.7</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>326976193.4</c:v>
+                  <c:v>105478512.77</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>340853607.48</c:v>
+                  <c:v>111537084.95</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>354662604.16</c:v>
+                  <c:v>117586549.46</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>368402579.38</c:v>
+                  <c:v>123621251.43</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>382072995.75</c:v>
+                  <c:v>129639287.05</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>395673350.53</c:v>
+                  <c:v>135636342.98</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>409203174.8</c:v>
+                  <c:v>141611636.91</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>422662182.26</c:v>
+                  <c:v>147561717.55</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>436049967.12</c:v>
+                  <c:v>153486543.64</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>449366243.5</c:v>
+                  <c:v>159384829.56</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>462610666.27</c:v>
+                  <c:v>165253934.06</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>475782978.24</c:v>
+                  <c:v>171094482.96</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>488882805.4</c:v>
+                  <c:v>176904151.87</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>501909918.39</c:v>
+                  <c:v>182683860.43</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>514864000.6</c:v>
+                  <c:v>188431500.22</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>527744791.92</c:v>
+                  <c:v>194148157.07</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>540551974.9</c:v>
+                  <c:v>199831843.99</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>553285287.8</c:v>
+                  <c:v>205483777</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>565944467.66</c:v>
+                  <c:v>211102084.22</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>578529167.91</c:v>
+                  <c:v>216688050.12</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>591135196.8099999</c:v>
+                  <c:v>222284199.97</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>603762554.36</c:v>
+                  <c:v>227890423.97</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>616411295.46</c:v>
+                  <c:v>233506694.67</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>629081447.5599999</c:v>
+                  <c:v>239132929.72</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>641773038.11</c:v>
+                  <c:v>244769129.12</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>654486149.46</c:v>
+                  <c:v>250415237.97</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>667220781.61</c:v>
+                  <c:v>256071256.27</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>679976962.01</c:v>
+                  <c:v>261737156.57</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>692754718.11</c:v>
+                  <c:v>267412966.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6858,7 +6909,7 @@
   <sheetPr>
     <tabColor rgb="FFE0B800"/>
   </sheetPr>
-  <dimension ref="B2:F92"/>
+  <dimension ref="B2:F91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -7083,182 +7134,190 @@
       <c r="B25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="8">
-        <v>0.3</v>
+      <c r="C25" s="7">
+        <v>0.5</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="C27" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>52</v>
-      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C31" s="8">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C32" s="8">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="7">
+        <v>24</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="7">
-        <v>18</v>
-      </c>
-      <c r="D33" s="6" t="s">
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="8">
+        <v>0.45</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="C36" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="11" t="s">
         <v>62</v>
+      </c>
+      <c r="C37" s="7">
+        <v>18</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="4" t="s">
+    <row r="39" spans="2:4">
+      <c r="B39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="7">
-        <v>6</v>
-      </c>
-      <c r="D38" s="6" t="s">
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="7">
-        <v>12</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>69</v>
-      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="7">
+        <v>6</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="D41" s="6" t="s">
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" s="10" t="s">
+      <c r="C43" s="7">
+        <v>12</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="12" t="s">
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" s="12" t="s">
+      <c r="C44" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
     </row>
     <row r="45" spans="2:4">
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="12" t="s">
@@ -7281,152 +7340,112 @@
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
     </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+    </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="6" t="s">
+      <c r="B51" s="12" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="4" t="s">
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="7">
         <v>3</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" s="7">
-        <v>24</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-    </row>
-    <row r="56" spans="2:6" ht="30" customHeight="1">
-      <c r="B56" s="13" t="s">
+      <c r="D56" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="13" t="s">
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="C57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="13" t="s">
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F56" s="13" t="s">
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+    </row>
+    <row r="60" spans="2:6" ht="30" customHeight="1">
+      <c r="B60" s="13" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="5" t="s">
+      <c r="C60" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C57" s="7">
-        <v>11.5</v>
-      </c>
-      <c r="D57" s="8">
-        <v>0.158</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F57" s="11" t="s">
+      <c r="D60" s="13" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="5" t="s">
+      <c r="E60" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C58" s="7">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D58" s="8">
-        <v>0.119</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="5" t="s">
+      <c r="F60" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="C59" s="7">
-        <v>5.5</v>
-      </c>
-      <c r="D59" s="8">
-        <v>0.075</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="7">
-        <v>4.6</v>
-      </c>
-      <c r="D60" s="8">
-        <v>0.063</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C61" s="7">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="D61" s="8">
-        <v>0.062</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.3</v>
+        <v>0.158</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>97</v>
@@ -7434,16 +7453,16 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C62" s="7">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D62" s="8">
-        <v>0.041</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.35</v>
+        <v>0.119</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>97</v>
@@ -7451,16 +7470,16 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C63" s="7">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="D63" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="E63" s="8">
-        <v>0.35</v>
+        <v>0.075</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>97</v>
@@ -7468,53 +7487,53 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C64" s="7">
+        <v>4.6</v>
+      </c>
+      <c r="D64" s="8">
+        <v>0.063</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="C64" s="7">
-        <v>3</v>
-      </c>
-      <c r="D64" s="8">
-        <v>0.041</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C65" s="7">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="D65" s="8">
-        <v>0.021</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.2</v>
+        <v>0.062</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C66" s="7">
+        <v>26.8</v>
+      </c>
+      <c r="D66" s="8">
+        <v>0.368</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="C66" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="D66" s="8">
-        <v>0.012</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="67" spans="2:6">
@@ -7711,21 +7730,21 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" s="4" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="C87" s="8">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="D87" s="8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E87" s="8">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="88" spans="2:5">
       <c r="B88" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C88" s="8">
         <v>0.4</v>
@@ -7739,7 +7758,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C89" s="8">
         <v>0.35</v>
@@ -7753,7 +7772,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C90" s="8">
         <v>0.01</v>
@@ -7767,51 +7786,39 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C91" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="D91" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="E91" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5">
-      <c r="B92" s="4" t="s">
+      <c r="D91" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C92" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="D92" s="8">
-        <v>0.3</v>
-      </c>
-      <c r="E92" s="8">
-        <v>0.4</v>
+      <c r="E91" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="28">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B59:F59"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B68:F68"/>
     <mergeCell ref="B69:F69"/>
@@ -7841,7 +7848,7 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7851,30 +7858,30 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D5" s="14">
         <v>0.42</v>
@@ -7891,10 +7898,10 @@
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D6" s="14">
         <v>0.35</v>
@@ -7906,15 +7913,15 @@
         <v>129000000</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D7" s="14">
         <v>0.15</v>
@@ -7926,15 +7933,15 @@
         <v>47000000</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" s="14">
         <v>0.08</v>
@@ -7946,12 +7953,12 @@
         <v>21500000</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" s="14">
         <v>1</v>
@@ -7962,7 +7969,7 @@
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -7972,10 +7979,10 @@
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -7984,10 +7991,10 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -7996,10 +8003,10 @@
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
@@ -8008,10 +8015,10 @@
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
@@ -8020,10 +8027,10 @@
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -8032,10 +8039,10 @@
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -8072,7 +8079,7 @@
   <sheetData>
     <row r="2" spans="2:12">
       <c r="B2" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -8086,19 +8093,19 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I4" s="17"/>
     </row>
@@ -8108,56 +8115,56 @@
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18">
-        <v>1112670380.27</v>
+        <v>1112634932.05</v>
       </c>
       <c r="E5" s="18"/>
       <c r="F5" s="18">
-        <v>7161404580.38</v>
+        <v>7161575518.4</v>
       </c>
       <c r="G5" s="18"/>
       <c r="H5" s="19">
-        <v>-0.4302067002390985</v>
+        <v>-0.4302248531068324</v>
       </c>
       <c r="I5" s="19"/>
     </row>
     <row r="8" spans="2:12" ht="35" customHeight="1">
       <c r="B8" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="2:12">
       <c r="B9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C9" s="21">
         <v>-12</v>
@@ -8192,7 +8199,7 @@
     </row>
     <row r="10" spans="2:12">
       <c r="B10" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C10" s="23">
         <v>-11</v>
@@ -8227,7 +8234,7 @@
     </row>
     <row r="11" spans="2:12">
       <c r="B11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C11" s="21">
         <v>-10</v>
@@ -8262,7 +8269,7 @@
     </row>
     <row r="12" spans="2:12">
       <c r="B12" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C12" s="23">
         <v>-9</v>
@@ -8297,7 +8304,7 @@
     </row>
     <row r="13" spans="2:12">
       <c r="B13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="21">
         <v>-8</v>
@@ -8332,7 +8339,7 @@
     </row>
     <row r="14" spans="2:12">
       <c r="B14" s="22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C14" s="23">
         <v>-7</v>
@@ -8367,7 +8374,7 @@
     </row>
     <row r="15" spans="2:12">
       <c r="B15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C15" s="21">
         <v>-6</v>
@@ -8402,7 +8409,7 @@
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="23">
         <v>-5</v>
@@ -8437,7 +8444,7 @@
     </row>
     <row r="17" spans="2:12">
       <c r="B17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="21">
         <v>-4</v>
@@ -8472,7 +8479,7 @@
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="23">
         <v>-3</v>
@@ -8507,7 +8514,7 @@
     </row>
     <row r="19" spans="2:12">
       <c r="B19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="21">
         <v>-2</v>
@@ -8542,7 +8549,7 @@
     </row>
     <row r="20" spans="2:12">
       <c r="B20" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C20" s="23">
         <v>-1</v>
@@ -8577,7 +8584,7 @@
     </row>
     <row r="21" spans="2:12">
       <c r="B21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C21" s="21">
         <v>0</v>
@@ -8612,7 +8619,7 @@
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C22" s="23">
         <v>1</v>
@@ -8633,21 +8640,21 @@
         <v>89.20999999999999</v>
       </c>
       <c r="I22" s="25">
-        <v>143203548.15</v>
+        <v>143199535.16</v>
       </c>
       <c r="J22" s="23">
         <v>167796</v>
       </c>
       <c r="K22" s="25">
-        <v>21734717.85</v>
+        <v>21738730.84</v>
       </c>
       <c r="L22" s="25">
-        <v>21734717.85</v>
+        <v>21738730.84</v>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C23" s="21">
         <v>2</v>
@@ -8668,21 +8675,21 @@
         <v>86.92</v>
       </c>
       <c r="I23" s="16">
-        <v>125211203.17</v>
+        <v>125204000.92</v>
       </c>
       <c r="J23" s="21">
         <v>310383</v>
       </c>
       <c r="K23" s="16">
-        <v>40001928.83</v>
+        <v>40009131.08</v>
       </c>
       <c r="L23" s="16">
-        <v>61736646.68</v>
+        <v>61747861.92</v>
       </c>
     </row>
     <row r="24" spans="2:12">
       <c r="B24" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C24" s="23">
         <v>3</v>
@@ -8703,21 +8710,21 @@
         <v>84.64</v>
       </c>
       <c r="I24" s="25">
-        <v>110101876.8</v>
+        <v>110105128.96</v>
       </c>
       <c r="J24" s="23">
         <v>431590</v>
       </c>
       <c r="K24" s="25">
-        <v>55386670.2</v>
+        <v>55383418.04</v>
       </c>
       <c r="L24" s="25">
-        <v>117123316.88</v>
+        <v>117131279.96</v>
       </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" s="21">
         <v>4</v>
@@ -8747,12 +8754,12 @@
         <v>68376147.45</v>
       </c>
       <c r="L25" s="16">
-        <v>185499464.33</v>
+        <v>185507427.41</v>
       </c>
     </row>
     <row r="26" spans="2:12">
       <c r="B26" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="23">
         <v>5</v>
@@ -8773,21 +8780,21 @@
         <v>80.06</v>
       </c>
       <c r="I26" s="25">
-        <v>86664213.56</v>
+        <v>86661507.42</v>
       </c>
       <c r="J26" s="23">
         <v>622365</v>
       </c>
       <c r="K26" s="25">
-        <v>79376352.94</v>
+        <v>79379059.08</v>
       </c>
       <c r="L26" s="25">
-        <v>264875817.27</v>
+        <v>264886486.49</v>
       </c>
     </row>
     <row r="27" spans="2:12">
       <c r="B27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C27" s="21">
         <v>6</v>
@@ -8808,21 +8815,21 @@
         <v>77.77</v>
       </c>
       <c r="I27" s="16">
-        <v>77592073.2</v>
+        <v>77587084.95999999</v>
       </c>
       <c r="J27" s="21">
         <v>697023</v>
       </c>
       <c r="K27" s="16">
-        <v>88725280.8</v>
+        <v>88730269.04000001</v>
       </c>
       <c r="L27" s="16">
-        <v>353601098.07</v>
+        <v>353616755.53</v>
       </c>
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C28" s="23">
         <v>7</v>
@@ -8843,21 +8850,21 @@
         <v>77.77</v>
       </c>
       <c r="I28" s="25">
-        <v>70825259.31999999</v>
+        <v>70820706.11</v>
       </c>
       <c r="J28" s="23">
         <v>773552</v>
       </c>
       <c r="K28" s="25">
-        <v>95769248.18000001</v>
+        <v>95773801.39</v>
       </c>
       <c r="L28" s="25">
-        <v>449370346.25</v>
+        <v>449390556.92</v>
       </c>
     </row>
     <row r="29" spans="2:12">
       <c r="B29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" s="21">
         <v>8</v>
@@ -8878,21 +8885,21 @@
         <v>77.77</v>
       </c>
       <c r="I29" s="16">
-        <v>65276401.95</v>
+        <v>65272205.46</v>
       </c>
       <c r="J29" s="21">
         <v>836775</v>
       </c>
       <c r="K29" s="16">
-        <v>101595808.05</v>
+        <v>101600004.54</v>
       </c>
       <c r="L29" s="16">
-        <v>550966154.3</v>
+        <v>550990561.46</v>
       </c>
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C30" s="23">
         <v>9</v>
@@ -8913,21 +8920,21 @@
         <v>77.77</v>
       </c>
       <c r="I30" s="25">
-        <v>60733253.1</v>
+        <v>60729348.68</v>
       </c>
       <c r="J30" s="23">
         <v>889011</v>
       </c>
       <c r="K30" s="25">
-        <v>106417025.4</v>
+        <v>106420929.82</v>
       </c>
       <c r="L30" s="25">
-        <v>657383179.6999999</v>
+        <v>657411491.28</v>
       </c>
     </row>
     <row r="31" spans="2:12">
       <c r="B31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C31" s="21">
         <v>10</v>
@@ -8948,21 +8955,21 @@
         <v>77.77</v>
       </c>
       <c r="I31" s="16">
-        <v>57019885.72</v>
+        <v>57016220.03</v>
       </c>
       <c r="J31" s="21">
         <v>932182</v>
       </c>
       <c r="K31" s="16">
-        <v>110409010.28</v>
+        <v>110412675.97</v>
       </c>
       <c r="L31" s="16">
-        <v>767792189.9799999</v>
+        <v>767824167.25</v>
       </c>
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C32" s="23">
         <v>11</v>
@@ -8983,21 +8990,21 @@
         <v>77.77</v>
       </c>
       <c r="I32" s="25">
-        <v>53990627.25</v>
+        <v>53987156.3</v>
       </c>
       <c r="J32" s="23">
         <v>967881</v>
       </c>
       <c r="K32" s="25">
-        <v>113717343.75</v>
+        <v>113720814.7</v>
       </c>
       <c r="L32" s="25">
-        <v>881509533.7299999</v>
+        <v>881544981.95</v>
       </c>
     </row>
     <row r="33" spans="2:12">
       <c r="B33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C33" s="21">
         <v>12</v>
@@ -9018,21 +9025,21 @@
         <v>77.77</v>
       </c>
       <c r="I33" s="16">
-        <v>51524848.65</v>
+        <v>51521536.22</v>
       </c>
       <c r="J33" s="21">
         <v>997425</v>
       </c>
       <c r="K33" s="16">
-        <v>116462654.85</v>
+        <v>116465967.28</v>
       </c>
       <c r="L33" s="16">
-        <v>997972188.5799999</v>
+        <v>998010949.23</v>
       </c>
     </row>
     <row r="34" spans="2:12">
       <c r="B34" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C34" s="23">
         <v>13</v>
@@ -9053,21 +9060,21 @@
         <v>77.77</v>
       </c>
       <c r="I34" s="25">
-        <v>49963204.42</v>
+        <v>49959992.39</v>
       </c>
       <c r="J34" s="23">
         <v>1017094</v>
       </c>
       <c r="K34" s="25">
-        <v>118304197.58</v>
+        <v>118307409.61</v>
       </c>
       <c r="L34" s="25">
-        <v>1116276386.16</v>
+        <v>1116318358.84</v>
       </c>
     </row>
     <row r="35" spans="2:12">
       <c r="B35" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C35" s="21">
         <v>14</v>
@@ -9088,21 +9095,21 @@
         <v>77.77</v>
       </c>
       <c r="I35" s="16">
-        <v>48649273.57</v>
+        <v>48646146.01</v>
       </c>
       <c r="J35" s="21">
         <v>1034059</v>
       </c>
       <c r="K35" s="16">
-        <v>119898575.93</v>
+        <v>119901703.49</v>
       </c>
       <c r="L35" s="16">
-        <v>1236174962.09</v>
+        <v>1236220062.33</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="B36" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C36" s="23">
         <v>15</v>
@@ -9123,21 +9130,21 @@
         <v>77.77</v>
       </c>
       <c r="I36" s="25">
-        <v>47545335.22</v>
+        <v>47542278.63</v>
       </c>
       <c r="J36" s="23">
         <v>1048734</v>
       </c>
       <c r="K36" s="25">
-        <v>121283510.78</v>
+        <v>121286567.37</v>
       </c>
       <c r="L36" s="25">
-        <v>1357458472.87</v>
+        <v>1357506629.7</v>
       </c>
     </row>
     <row r="37" spans="2:12">
       <c r="B37" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="21">
         <v>16</v>
@@ -9158,21 +9165,21 @@
         <v>77.77</v>
       </c>
       <c r="I37" s="16">
-        <v>46619579.4</v>
+        <v>46616582.32</v>
       </c>
       <c r="J37" s="21">
         <v>1061465</v>
       </c>
       <c r="K37" s="16">
-        <v>122490629.1</v>
+        <v>122493626.18</v>
       </c>
       <c r="L37" s="16">
-        <v>1479949101.97</v>
+        <v>1480000255.88</v>
       </c>
     </row>
     <row r="38" spans="2:12">
       <c r="B38" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C38" s="23">
         <v>17</v>
@@ -9193,21 +9200,21 @@
         <v>77.77</v>
       </c>
       <c r="I38" s="25">
-        <v>45844940.4</v>
+        <v>45841993.12</v>
       </c>
       <c r="J38" s="23">
         <v>1072549</v>
       </c>
       <c r="K38" s="25">
-        <v>123547088.1</v>
+        <v>123550035.38</v>
       </c>
       <c r="L38" s="25">
-        <v>1603496190.07</v>
+        <v>1603550291.26</v>
       </c>
     </row>
     <row r="39" spans="2:12">
       <c r="B39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C39" s="21">
         <v>18</v>
@@ -9228,21 +9235,21 @@
         <v>77.77</v>
       </c>
       <c r="I39" s="16">
-        <v>45198474.6</v>
+        <v>45195568.88</v>
       </c>
       <c r="J39" s="21">
         <v>1082237</v>
       </c>
       <c r="K39" s="16">
-        <v>124475922.9</v>
+        <v>124478828.62</v>
       </c>
       <c r="L39" s="16">
-        <v>1727972112.97</v>
+        <v>1728029119.88</v>
       </c>
     </row>
     <row r="40" spans="2:12">
       <c r="B40" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C40" s="23">
         <v>19</v>
@@ -9263,21 +9270,21 @@
         <v>77.77</v>
       </c>
       <c r="I40" s="25">
-        <v>44660816.02</v>
+        <v>44657944.87</v>
       </c>
       <c r="J40" s="23">
         <v>1090740</v>
       </c>
       <c r="K40" s="25">
-        <v>125296316.47</v>
+        <v>125299187.63</v>
       </c>
       <c r="L40" s="25">
-        <v>1853268429.44</v>
+        <v>1853328307.51</v>
       </c>
     </row>
     <row r="41" spans="2:12">
       <c r="B41" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C41" s="21">
         <v>20</v>
@@ -9298,21 +9305,21 @@
         <v>77.77</v>
       </c>
       <c r="I41" s="16">
-        <v>44215320.82</v>
+        <v>44212478.31</v>
       </c>
       <c r="J41" s="21">
         <v>1098241</v>
       </c>
       <c r="K41" s="16">
-        <v>126025095.68</v>
+        <v>126027938.19</v>
       </c>
       <c r="L41" s="16">
-        <v>1979293525.12</v>
+        <v>1979356245.7</v>
       </c>
     </row>
     <row r="42" spans="2:12">
       <c r="B42" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C42" s="23">
         <v>21</v>
@@ -9333,21 +9340,21 @@
         <v>77.77</v>
       </c>
       <c r="I42" s="25">
-        <v>43848067.27</v>
+        <v>43845248.37</v>
       </c>
       <c r="J42" s="23">
         <v>1104890</v>
       </c>
       <c r="K42" s="25">
-        <v>126676090.72</v>
+        <v>126678909.63</v>
       </c>
       <c r="L42" s="25">
-        <v>2105969615.84</v>
+        <v>2106035155.33</v>
       </c>
     </row>
     <row r="43" spans="2:12">
       <c r="B43" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C43" s="21">
         <v>22</v>
@@ -9368,21 +9375,21 @@
         <v>77.77</v>
       </c>
       <c r="I43" s="16">
-        <v>43547155.8</v>
+        <v>43544356.24</v>
       </c>
       <c r="J43" s="21">
         <v>1110818</v>
       </c>
       <c r="K43" s="16">
-        <v>127261201.2</v>
+        <v>127264000.76</v>
       </c>
       <c r="L43" s="16">
-        <v>2233230817.04</v>
+        <v>2233299156.09</v>
       </c>
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C44" s="23">
         <v>23</v>
@@ -9403,21 +9410,21 @@
         <v>77.77</v>
       </c>
       <c r="I44" s="25">
-        <v>43302553.42</v>
+        <v>43299769.59</v>
       </c>
       <c r="J44" s="23">
         <v>1116136</v>
       </c>
       <c r="K44" s="25">
-        <v>127790460.08</v>
+        <v>127793243.91</v>
       </c>
       <c r="L44" s="25">
-        <v>2361021277.12</v>
+        <v>2361092400</v>
       </c>
     </row>
     <row r="45" spans="2:12">
       <c r="B45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C45" s="21">
         <v>24</v>
@@ -9438,21 +9445,21 @@
         <v>77.77</v>
       </c>
       <c r="I45" s="16">
-        <v>43105782.67</v>
+        <v>43103011.49</v>
       </c>
       <c r="J45" s="21">
         <v>1120936</v>
       </c>
       <c r="K45" s="16">
-        <v>128272436.33</v>
+        <v>128275207.51</v>
       </c>
       <c r="L45" s="16">
-        <v>2489293713.45</v>
+        <v>2489367607.51</v>
       </c>
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C46" s="23">
         <v>25</v>
@@ -9473,21 +9480,21 @@
         <v>77.77</v>
       </c>
       <c r="I46" s="25">
-        <v>42949532.7</v>
+        <v>42946771.56</v>
       </c>
       <c r="J46" s="23">
         <v>1125297</v>
       </c>
       <c r="K46" s="25">
-        <v>128714257.8</v>
+        <v>128717018.94</v>
       </c>
       <c r="L46" s="25">
-        <v>2618007971.25</v>
+        <v>2618084626.45</v>
       </c>
     </row>
     <row r="47" spans="2:12">
       <c r="B47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C47" s="21">
         <v>26</v>
@@ -9508,21 +9515,21 @@
         <v>77.77</v>
       </c>
       <c r="I47" s="16">
-        <v>42827659.27</v>
+        <v>42824905.97</v>
       </c>
       <c r="J47" s="21">
         <v>1129287</v>
       </c>
       <c r="K47" s="16">
-        <v>129122251.72</v>
+        <v>129125005.03</v>
       </c>
       <c r="L47" s="16">
-        <v>2747130222.97</v>
+        <v>2747209631.48</v>
       </c>
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C48" s="23">
         <v>27</v>
@@ -9543,21 +9550,21 @@
         <v>77.77</v>
       </c>
       <c r="I48" s="25">
-        <v>42734951.47</v>
+        <v>42732204.13</v>
       </c>
       <c r="J48" s="23">
         <v>1132962</v>
       </c>
       <c r="K48" s="25">
-        <v>129501537.53</v>
+        <v>129504284.87</v>
       </c>
       <c r="L48" s="25">
-        <v>2876631760.5</v>
+        <v>2876713916.35</v>
       </c>
     </row>
     <row r="49" spans="2:12">
       <c r="B49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C49" s="21">
         <v>28</v>
@@ -9578,21 +9585,21 @@
         <v>77.77</v>
       </c>
       <c r="I49" s="16">
-        <v>42666976.12</v>
+        <v>42664233.15</v>
       </c>
       <c r="J49" s="21">
         <v>1136371</v>
       </c>
       <c r="K49" s="16">
-        <v>129856548.38</v>
+        <v>129859291.35</v>
       </c>
       <c r="L49" s="16">
-        <v>3006488308.88</v>
+        <v>3006573207.7</v>
       </c>
     </row>
     <row r="50" spans="2:12">
       <c r="B50" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C50" s="23">
         <v>29</v>
@@ -9613,21 +9620,21 @@
         <v>77.77</v>
       </c>
       <c r="I50" s="25">
-        <v>42620077.8</v>
+        <v>42617337.84</v>
       </c>
       <c r="J50" s="23">
         <v>1139555</v>
       </c>
       <c r="K50" s="25">
-        <v>130191031.2</v>
+        <v>130193771.16</v>
       </c>
       <c r="L50" s="25">
-        <v>3136679340.08</v>
+        <v>3136766978.86</v>
       </c>
     </row>
     <row r="51" spans="2:12">
       <c r="B51" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" s="21">
         <v>30</v>
@@ -9648,21 +9655,21 @@
         <v>77.77</v>
       </c>
       <c r="I51" s="16">
-        <v>42591067.72</v>
+        <v>42588329.63</v>
       </c>
       <c r="J51" s="21">
         <v>1142548</v>
       </c>
       <c r="K51" s="16">
-        <v>130508083.28</v>
+        <v>130510821.37</v>
       </c>
       <c r="L51" s="16">
-        <v>3267187423.36</v>
+        <v>3267277800.23</v>
       </c>
     </row>
     <row r="52" spans="2:12">
       <c r="B52" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C52" s="23">
         <v>31</v>
@@ -9683,21 +9690,21 @@
         <v>77.77</v>
       </c>
       <c r="I52" s="25">
-        <v>42577146</v>
+        <v>42574408.8</v>
       </c>
       <c r="J52" s="23">
         <v>1145380</v>
       </c>
       <c r="K52" s="25">
-        <v>130810504.5</v>
+        <v>130813241.7</v>
       </c>
       <c r="L52" s="25">
-        <v>3397997927.86</v>
+        <v>3398091041.93</v>
       </c>
     </row>
     <row r="53" spans="2:12">
       <c r="B53" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C53" s="21">
         <v>32</v>
@@ -9718,21 +9725,21 @@
         <v>77.77</v>
       </c>
       <c r="I53" s="16">
-        <v>42576134.92</v>
+        <v>42573397.79</v>
       </c>
       <c r="J53" s="21">
         <v>1148076</v>
       </c>
       <c r="K53" s="16">
-        <v>131100472.58</v>
+        <v>131103209.71</v>
       </c>
       <c r="L53" s="16">
-        <v>3529098400.44</v>
+        <v>3529194251.64</v>
       </c>
     </row>
     <row r="54" spans="2:12">
       <c r="B54" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C54" s="23">
         <v>33</v>
@@ -9753,21 +9760,21 @@
         <v>77.77</v>
       </c>
       <c r="I54" s="25">
-        <v>42586012.35</v>
+        <v>42583274.58</v>
       </c>
       <c r="J54" s="23">
         <v>1150657</v>
       </c>
       <c r="K54" s="25">
-        <v>131380009.65</v>
+        <v>131382747.42</v>
       </c>
       <c r="L54" s="25">
-        <v>3660478410.09</v>
+        <v>3660576999.06</v>
       </c>
     </row>
     <row r="55" spans="2:12">
       <c r="B55" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C55" s="21">
         <v>34</v>
@@ -9788,21 +9795,21 @@
         <v>77.77</v>
       </c>
       <c r="I55" s="16">
-        <v>42605222.77</v>
+        <v>42602483.77</v>
       </c>
       <c r="J55" s="21">
         <v>1153140</v>
       </c>
       <c r="K55" s="16">
-        <v>131650762.72</v>
+        <v>131653501.73</v>
       </c>
       <c r="L55" s="16">
-        <v>3792129172.81</v>
+        <v>3792230500.79</v>
       </c>
     </row>
     <row r="56" spans="2:12">
       <c r="B56" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C56" s="23">
         <v>35</v>
@@ -9823,21 +9830,21 @@
         <v>77.77</v>
       </c>
       <c r="I56" s="25">
-        <v>42632288.47</v>
+        <v>42629547.73</v>
       </c>
       <c r="J56" s="23">
         <v>1155542</v>
       </c>
       <c r="K56" s="25">
-        <v>131914118.03</v>
+        <v>131916858.77</v>
       </c>
       <c r="L56" s="25">
-        <v>3924043290.84</v>
+        <v>3924147359.56</v>
       </c>
     </row>
     <row r="57" spans="2:12">
       <c r="B57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C57" s="21">
         <v>36</v>
@@ -9858,21 +9865,21 @@
         <v>77.77</v>
       </c>
       <c r="I57" s="16">
-        <v>42666120.6</v>
+        <v>42663377.68</v>
       </c>
       <c r="J57" s="21">
         <v>1157875</v>
       </c>
       <c r="K57" s="16">
-        <v>132171255.9</v>
+        <v>132173998.82</v>
       </c>
       <c r="L57" s="16">
-        <v>4056214546.74</v>
+        <v>4056321358.38</v>
       </c>
     </row>
     <row r="58" spans="2:12">
       <c r="B58" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C58" s="23">
         <v>37</v>
@@ -9893,21 +9900,21 @@
         <v>77.77</v>
       </c>
       <c r="I58" s="25">
-        <v>42705630.3</v>
+        <v>42702884.84</v>
       </c>
       <c r="J58" s="23">
         <v>1160150</v>
       </c>
       <c r="K58" s="25">
-        <v>132423082.2</v>
+        <v>132425827.66</v>
       </c>
       <c r="L58" s="25">
-        <v>4188637628.94</v>
+        <v>4188747186.04</v>
       </c>
     </row>
     <row r="59" spans="2:12">
       <c r="B59" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C59" s="21">
         <v>38</v>
@@ -9928,21 +9935,21 @@
         <v>77.77</v>
       </c>
       <c r="I59" s="16">
-        <v>42750039.82</v>
+        <v>42747291.51</v>
       </c>
       <c r="J59" s="21">
         <v>1162376</v>
       </c>
       <c r="K59" s="16">
-        <v>132670557.68</v>
+        <v>132673305.99</v>
       </c>
       <c r="L59" s="16">
-        <v>4321308186.62</v>
+        <v>4321420492.03</v>
       </c>
     </row>
     <row r="60" spans="2:12">
       <c r="B60" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C60" s="23">
         <v>39</v>
@@ -9963,21 +9970,21 @@
         <v>77.77</v>
       </c>
       <c r="I60" s="25">
-        <v>42798571.42</v>
+        <v>42795819.99</v>
       </c>
       <c r="J60" s="23">
         <v>1164562</v>
       </c>
       <c r="K60" s="25">
-        <v>132914460.08</v>
+        <v>132917211.51</v>
       </c>
       <c r="L60" s="25">
-        <v>4454222646.7</v>
+        <v>4454337703.54</v>
       </c>
     </row>
     <row r="61" spans="2:12">
       <c r="B61" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C61" s="21">
         <v>40</v>
@@ -9998,21 +10005,21 @@
         <v>77.77</v>
       </c>
       <c r="I61" s="16">
-        <v>42850680.67</v>
+        <v>42847925.89</v>
       </c>
       <c r="J61" s="21">
         <v>1166713</v>
       </c>
       <c r="K61" s="16">
-        <v>133155150.83</v>
+        <v>133157905.61</v>
       </c>
       <c r="L61" s="16">
-        <v>4587377797.53</v>
+        <v>4587495609.15</v>
       </c>
     </row>
     <row r="62" spans="2:12">
       <c r="B62" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C62" s="23">
         <v>41</v>
@@ -10033,21 +10040,21 @@
         <v>77.77</v>
       </c>
       <c r="I62" s="25">
-        <v>42905745.37</v>
+        <v>42902987.05</v>
       </c>
       <c r="J62" s="23">
         <v>1168836</v>
       </c>
       <c r="K62" s="25">
-        <v>133393435.12</v>
+        <v>133396193.45</v>
       </c>
       <c r="L62" s="25">
-        <v>4720771232.65</v>
+        <v>4720891802.599999</v>
       </c>
     </row>
     <row r="63" spans="2:12">
       <c r="B63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C63" s="21">
         <v>42</v>
@@ -10068,21 +10075,21 @@
         <v>77.77</v>
       </c>
       <c r="I63" s="16">
-        <v>42963376.65</v>
+        <v>42960614.62</v>
       </c>
       <c r="J63" s="21">
         <v>1170936</v>
       </c>
       <c r="K63" s="16">
-        <v>133629610.35</v>
+        <v>133632372.38</v>
       </c>
       <c r="L63" s="16">
-        <v>4854400843</v>
+        <v>4854524174.98</v>
       </c>
     </row>
     <row r="64" spans="2:12">
       <c r="B64" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C64" s="23">
         <v>43</v>
@@ -10103,21 +10110,21 @@
         <v>77.77</v>
       </c>
       <c r="I64" s="25">
-        <v>43023263.4</v>
+        <v>43020497.52</v>
       </c>
       <c r="J64" s="23">
         <v>1173016</v>
       </c>
       <c r="K64" s="25">
-        <v>133864079.1</v>
+        <v>133866844.98</v>
       </c>
       <c r="L64" s="25">
-        <v>4988264922.1</v>
+        <v>4988391019.959999</v>
       </c>
     </row>
     <row r="65" spans="2:12">
       <c r="B65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C65" s="21">
         <v>44</v>
@@ -10138,21 +10145,21 @@
         <v>77.77</v>
       </c>
       <c r="I65" s="16">
-        <v>43084938.97</v>
+        <v>43082169.13</v>
       </c>
       <c r="J65" s="21">
         <v>1175080</v>
       </c>
       <c r="K65" s="16">
-        <v>134097216.53</v>
+        <v>134099986.37</v>
       </c>
       <c r="L65" s="16">
-        <v>5122362138.63</v>
+        <v>5122491006.329999</v>
       </c>
     </row>
     <row r="66" spans="2:12">
       <c r="B66" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C66" s="23">
         <v>45</v>
@@ -10173,21 +10180,21 @@
         <v>77.77</v>
       </c>
       <c r="I66" s="25">
-        <v>43148325.6</v>
+        <v>43145551.68</v>
       </c>
       <c r="J66" s="23">
         <v>1177131</v>
       </c>
       <c r="K66" s="25">
-        <v>134329100.4</v>
+        <v>134331874.32</v>
       </c>
       <c r="L66" s="25">
-        <v>5256691239.03</v>
+        <v>5256822880.649999</v>
       </c>
     </row>
     <row r="67" spans="2:12">
       <c r="B67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C67" s="21">
         <v>46</v>
@@ -10208,21 +10215,21 @@
         <v>77.77</v>
       </c>
       <c r="I67" s="16">
-        <v>43213034.4</v>
+        <v>43210256.32</v>
       </c>
       <c r="J67" s="21">
         <v>1179171</v>
       </c>
       <c r="K67" s="16">
-        <v>134560211.1</v>
+        <v>134562989.18</v>
       </c>
       <c r="L67" s="16">
-        <v>5391251450.13</v>
+        <v>5391385869.829999</v>
       </c>
     </row>
     <row r="68" spans="2:12">
       <c r="B68" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C68" s="23">
         <v>47</v>
@@ -10243,21 +10250,21 @@
         <v>77.77</v>
       </c>
       <c r="I68" s="25">
-        <v>43278987.6</v>
+        <v>43276205.28</v>
       </c>
       <c r="J68" s="23">
         <v>1181203</v>
       </c>
       <c r="K68" s="25">
-        <v>134790534.9</v>
+        <v>134793317.22</v>
       </c>
       <c r="L68" s="25">
-        <v>5526041985.03</v>
+        <v>5526179187.049999</v>
       </c>
     </row>
     <row r="69" spans="2:12">
       <c r="B69" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C69" s="21">
         <v>48</v>
@@ -10278,21 +10285,21 @@
         <v>77.77</v>
       </c>
       <c r="I69" s="16">
-        <v>43345951.87</v>
+        <v>43343165.25</v>
       </c>
       <c r="J69" s="21">
         <v>1183228</v>
       </c>
       <c r="K69" s="16">
-        <v>135020396.62</v>
+        <v>135023183.25</v>
       </c>
       <c r="L69" s="16">
-        <v>5661062381.65</v>
+        <v>5661202370.299999</v>
       </c>
     </row>
     <row r="70" spans="2:12">
       <c r="B70" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C70" s="23">
         <v>49</v>
@@ -10313,21 +10320,21 @@
         <v>77.77</v>
       </c>
       <c r="I70" s="25">
-        <v>43413849.45</v>
+        <v>43411058.46</v>
       </c>
       <c r="J70" s="23">
         <v>1185248</v>
       </c>
       <c r="K70" s="25">
-        <v>135249782.55</v>
+        <v>135252573.54</v>
       </c>
       <c r="L70" s="25">
-        <v>5796312164.2</v>
+        <v>5796454943.839999</v>
       </c>
     </row>
     <row r="71" spans="2:12">
       <c r="B71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C71" s="21">
         <v>50</v>
@@ -10348,21 +10355,21 @@
         <v>77.77</v>
       </c>
       <c r="I71" s="16">
-        <v>43482524.77</v>
+        <v>43479729.37</v>
       </c>
       <c r="J71" s="21">
         <v>1187264</v>
       </c>
       <c r="K71" s="16">
-        <v>135478848.22</v>
+        <v>135481643.63</v>
       </c>
       <c r="L71" s="16">
-        <v>5931791012.42</v>
+        <v>5931936587.469999</v>
       </c>
     </row>
     <row r="72" spans="2:12">
       <c r="B72" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C72" s="23">
         <v>51</v>
@@ -10383,21 +10390,21 @@
         <v>77.77</v>
       </c>
       <c r="I72" s="25">
-        <v>43551822.3</v>
+        <v>43549022.44</v>
       </c>
       <c r="J72" s="23">
         <v>1189277</v>
       </c>
       <c r="K72" s="25">
-        <v>135707840.7</v>
+        <v>135710640.56</v>
       </c>
       <c r="L72" s="25">
-        <v>6067498853.12</v>
+        <v>6067647228.03</v>
       </c>
     </row>
     <row r="73" spans="2:12">
       <c r="B73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C73" s="21">
         <v>52</v>
@@ -10418,21 +10425,21 @@
         <v>77.77</v>
       </c>
       <c r="I73" s="16">
-        <v>43621742.02</v>
+        <v>43618937.67</v>
       </c>
       <c r="J73" s="21">
         <v>1191288</v>
       </c>
       <c r="K73" s="16">
-        <v>135936668.47</v>
+        <v>135939472.83</v>
       </c>
       <c r="L73" s="16">
-        <v>6203435521.59</v>
+        <v>6203586700.86</v>
       </c>
     </row>
     <row r="74" spans="2:12">
       <c r="B74" s="22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C74" s="23">
         <v>53</v>
@@ -10453,21 +10460,21 @@
         <v>77.77</v>
       </c>
       <c r="I74" s="25">
-        <v>43692206.17</v>
+        <v>43689397.29</v>
       </c>
       <c r="J74" s="23">
         <v>1193298</v>
       </c>
       <c r="K74" s="25">
-        <v>136165500.82</v>
+        <v>136168309.71</v>
       </c>
       <c r="L74" s="25">
-        <v>6339601022.41</v>
+        <v>6339755010.57</v>
       </c>
     </row>
     <row r="75" spans="2:12">
       <c r="B75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C75" s="21">
         <v>54</v>
@@ -10488,21 +10495,21 @@
         <v>77.77</v>
       </c>
       <c r="I75" s="16">
-        <v>43763059.2</v>
+        <v>43760245.76</v>
       </c>
       <c r="J75" s="21">
         <v>1195308</v>
       </c>
       <c r="K75" s="16">
-        <v>136394401.8</v>
+        <v>136397215.24</v>
       </c>
       <c r="L75" s="16">
-        <v>6475995424.21</v>
+        <v>6476152225.809999</v>
       </c>
     </row>
     <row r="76" spans="2:12">
       <c r="B76" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C76" s="23">
         <v>55</v>
@@ -10523,21 +10530,21 @@
         <v>77.77</v>
       </c>
       <c r="I76" s="25">
-        <v>43834378.87</v>
+        <v>43831560.85</v>
       </c>
       <c r="J76" s="23">
         <v>1197318</v>
       </c>
       <c r="K76" s="25">
-        <v>136623293.62</v>
+        <v>136626111.65</v>
       </c>
       <c r="L76" s="25">
-        <v>6612618717.83</v>
+        <v>6612778337.459999</v>
       </c>
     </row>
     <row r="77" spans="2:12">
       <c r="B77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C77" s="21">
         <v>56</v>
@@ -10558,21 +10565,21 @@
         <v>77.77</v>
       </c>
       <c r="I77" s="16">
-        <v>43906087.42</v>
+        <v>43903264.79</v>
       </c>
       <c r="J77" s="21">
         <v>1199329</v>
       </c>
       <c r="K77" s="16">
-        <v>136852345.57</v>
+        <v>136855168.21</v>
       </c>
       <c r="L77" s="16">
-        <v>6749471063.4</v>
+        <v>6749633505.669999</v>
       </c>
     </row>
     <row r="78" spans="2:12">
       <c r="B78" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C78" s="23">
         <v>57</v>
@@ -10593,21 +10600,21 @@
         <v>77.77</v>
       </c>
       <c r="I78" s="25">
-        <v>43978107.07</v>
+        <v>43975279.81</v>
       </c>
       <c r="J78" s="23">
         <v>1201340</v>
       </c>
       <c r="K78" s="25">
-        <v>137081635.43</v>
+        <v>137084462.69</v>
       </c>
       <c r="L78" s="25">
-        <v>6886552698.83</v>
+        <v>6886717968.359999</v>
       </c>
     </row>
     <row r="79" spans="2:12">
       <c r="B79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C79" s="21">
         <v>58</v>
@@ -10628,21 +10635,21 @@
         <v>77.77</v>
       </c>
       <c r="I79" s="16">
-        <v>44050360.05</v>
+        <v>44047528.14</v>
       </c>
       <c r="J79" s="21">
         <v>1203353</v>
       </c>
       <c r="K79" s="16">
-        <v>137311149.45</v>
+        <v>137313981.36</v>
       </c>
       <c r="L79" s="16">
-        <v>7023863848.28</v>
+        <v>7024031949.719998</v>
       </c>
     </row>
     <row r="80" spans="2:12">
       <c r="B80" s="22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C80" s="23">
         <v>59</v>
@@ -10663,16 +10670,16 @@
         <v>77.77</v>
       </c>
       <c r="I80" s="25">
-        <v>44123001.9</v>
+        <v>44120165.32</v>
       </c>
       <c r="J80" s="23">
         <v>1205368</v>
       </c>
       <c r="K80" s="25">
-        <v>137540732.1</v>
+        <v>137543568.68</v>
       </c>
       <c r="L80" s="25">
-        <v>7161404580.38</v>
+        <v>7161575518.399999</v>
       </c>
     </row>
   </sheetData>
@@ -10707,7 +10714,7 @@
   <sheetData>
     <row r="2" spans="2:16">
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -10723,51 +10730,51 @@
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I4" s="17"/>
       <c r="J4" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="26">
-        <v>67402845.31</v>
+        <v>10349792.95</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="26">
-        <v>940339624.1399999</v>
+        <v>373217288.4299999</v>
       </c>
       <c r="E5" s="26"/>
       <c r="F5" s="26">
-        <v>692754718.11</v>
+        <v>267412966.32</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="27">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="I5" s="27"/>
       <c r="J5" s="28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K5" s="28"/>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -10777,33 +10784,33 @@
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C8" s="27">
-        <v>0.4488724673100167</v>
+        <v>0.2257674041179913</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E8" s="27">
-        <v>0.2848367131681429</v>
+        <v>0.6438064779570211</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>265</v>
+        <v>132</v>
       </c>
       <c r="G8" s="27">
-        <v>0.2662908195218405</v>
+        <v>0.1304261179249876</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="35" customHeight="1">
       <c r="B10" s="29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E10" s="29" t="s">
         <v>266</v>
@@ -10821,10 +10828,10 @@
         <v>270</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L10" s="29" t="s">
         <v>271</v>
@@ -10844,7 +10851,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C11" s="21">
         <v>0</v>
@@ -10853,7 +10860,7 @@
         <v>4200000</v>
       </c>
       <c r="E11" s="21">
-        <v>9129</v>
+        <v>765</v>
       </c>
       <c r="F11" s="21">
         <v>0</v>
@@ -10862,10 +10869,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="21">
-        <v>9129</v>
+        <v>765</v>
       </c>
       <c r="I11" s="14">
-        <v>0.0022</v>
+        <v>0.0002</v>
       </c>
       <c r="J11" s="14">
         <v>0</v>
@@ -10874,24 +10881,24 @@
         <v>50.33</v>
       </c>
       <c r="L11" s="16">
-        <v>459416.93</v>
+        <v>38502.45</v>
       </c>
       <c r="M11" s="16">
-        <v>114854.23</v>
+        <v>9625.610000000001</v>
       </c>
       <c r="N11" s="16">
-        <v>-355437.31</v>
+        <v>-671123.16</v>
       </c>
       <c r="O11" s="16">
-        <v>459416.93</v>
+        <v>38502.45</v>
       </c>
       <c r="P11" s="16">
-        <v>-355437.31</v>
+        <v>-671123.16</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C12" s="23">
         <v>1</v>
@@ -10900,7 +10907,7 @@
         <v>4207000</v>
       </c>
       <c r="E12" s="23">
-        <v>12527</v>
+        <v>1259</v>
       </c>
       <c r="F12" s="23">
         <v>0</v>
@@ -10909,10 +10916,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="23">
-        <v>12527</v>
+        <v>1259</v>
       </c>
       <c r="I12" s="24">
-        <v>0.003</v>
+        <v>0.0003</v>
       </c>
       <c r="J12" s="24">
         <v>0</v>
@@ -10921,24 +10928,24 @@
         <v>50.05</v>
       </c>
       <c r="L12" s="25">
-        <v>626982.61</v>
+        <v>63012.95</v>
       </c>
       <c r="M12" s="25">
-        <v>156745.65</v>
+        <v>15753.24</v>
       </c>
       <c r="N12" s="25">
-        <v>270236.96</v>
+        <v>-152740.29</v>
       </c>
       <c r="O12" s="25">
-        <v>1086399.54</v>
+        <v>101515.4</v>
       </c>
       <c r="P12" s="25">
-        <v>-85200.35000000001</v>
+        <v>-823863.45</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C13" s="21">
         <v>2</v>
@@ -10947,7 +10954,7 @@
         <v>4214011</v>
       </c>
       <c r="E13" s="21">
-        <v>17073</v>
+        <v>2051</v>
       </c>
       <c r="F13" s="21">
         <v>0</v>
@@ -10956,10 +10963,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="21">
-        <v>17073</v>
+        <v>2051</v>
       </c>
       <c r="I13" s="14">
-        <v>0.0041</v>
+        <v>0.0005</v>
       </c>
       <c r="J13" s="14">
         <v>0</v>
@@ -10968,24 +10975,24 @@
         <v>49.78</v>
       </c>
       <c r="L13" s="16">
-        <v>849825.65</v>
+        <v>102098.78</v>
       </c>
       <c r="M13" s="16">
-        <v>212456.41</v>
+        <v>25524.69</v>
       </c>
       <c r="N13" s="16">
-        <v>437369.24</v>
+        <v>-123425.92</v>
       </c>
       <c r="O13" s="16">
-        <v>1936225.19</v>
+        <v>203614.18</v>
       </c>
       <c r="P13" s="16">
-        <v>352168.89</v>
+        <v>-947289.36</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C14" s="23">
         <v>3</v>
@@ -10994,7 +11001,7 @@
         <v>4221035</v>
       </c>
       <c r="E14" s="23">
-        <v>23061</v>
+        <v>3297</v>
       </c>
       <c r="F14" s="23">
         <v>0</v>
@@ -11003,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="23">
-        <v>23061</v>
+        <v>3297</v>
       </c>
       <c r="I14" s="24">
-        <v>0.0055</v>
+        <v>0.0008</v>
       </c>
       <c r="J14" s="24">
         <v>0</v>
@@ -11015,24 +11022,24 @@
         <v>49.5</v>
       </c>
       <c r="L14" s="25">
-        <v>1141554.09</v>
+        <v>163201.5</v>
       </c>
       <c r="M14" s="25">
-        <v>285388.52</v>
+        <v>40800.38</v>
       </c>
       <c r="N14" s="25">
-        <v>656165.5699999999</v>
+        <v>-77598.88</v>
       </c>
       <c r="O14" s="25">
-        <v>3077779.28</v>
+        <v>366815.68</v>
       </c>
       <c r="P14" s="25">
-        <v>1008334.46</v>
+        <v>-1024888.24</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C15" s="21">
         <v>4</v>
@@ -11041,19 +11048,19 @@
         <v>4228070</v>
       </c>
       <c r="E15" s="21">
-        <v>30786</v>
+        <v>5212</v>
       </c>
       <c r="F15" s="21">
         <v>0</v>
       </c>
       <c r="G15" s="21">
-        <v>2901</v>
+        <v>0</v>
       </c>
       <c r="H15" s="21">
-        <v>33687</v>
+        <v>5212</v>
       </c>
       <c r="I15" s="14">
-        <v>0.008</v>
+        <v>0.0012</v>
       </c>
       <c r="J15" s="14">
         <v>0</v>
@@ -11062,24 +11069,24 @@
         <v>49.23</v>
       </c>
       <c r="L15" s="16">
-        <v>1658309.95</v>
+        <v>256586.76</v>
       </c>
       <c r="M15" s="16">
-        <v>414577.49</v>
+        <v>64146.69</v>
       </c>
       <c r="N15" s="16">
-        <v>1043732.46</v>
+        <v>-7559.93</v>
       </c>
       <c r="O15" s="16">
-        <v>4736089.23</v>
+        <v>623402.4399999999</v>
       </c>
       <c r="P15" s="16">
-        <v>2052066.92</v>
+        <v>-1032448.17</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C16" s="23">
         <v>5</v>
@@ -11088,19 +11095,19 @@
         <v>4235116</v>
       </c>
       <c r="E16" s="23">
-        <v>40492</v>
+        <v>8074</v>
       </c>
       <c r="F16" s="23">
         <v>0</v>
       </c>
       <c r="G16" s="23">
-        <v>7632</v>
+        <v>0</v>
       </c>
       <c r="H16" s="23">
-        <v>48124</v>
+        <v>8074</v>
       </c>
       <c r="I16" s="24">
-        <v>0.0114</v>
+        <v>0.0019</v>
       </c>
       <c r="J16" s="24">
         <v>0</v>
@@ -11109,24 +11116,24 @@
         <v>48.95</v>
       </c>
       <c r="L16" s="25">
-        <v>2355790.11</v>
+        <v>395222.3</v>
       </c>
       <c r="M16" s="25">
-        <v>588947.53</v>
+        <v>98805.58</v>
       </c>
       <c r="N16" s="25">
-        <v>1566842.58</v>
+        <v>96416.73</v>
       </c>
       <c r="O16" s="25">
-        <v>7091879.34</v>
+        <v>1018624.74</v>
       </c>
       <c r="P16" s="25">
-        <v>3618909.5</v>
+        <v>-936031.45</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="21">
         <v>6</v>
@@ -11135,19 +11142,19 @@
         <v>4242175</v>
       </c>
       <c r="E17" s="21">
-        <v>52291</v>
+        <v>12200</v>
       </c>
       <c r="F17" s="21">
         <v>0</v>
       </c>
       <c r="G17" s="21">
-        <v>14785</v>
+        <v>0</v>
       </c>
       <c r="H17" s="21">
-        <v>67076</v>
+        <v>12200</v>
       </c>
       <c r="I17" s="14">
-        <v>0.0158</v>
+        <v>0.0029</v>
       </c>
       <c r="J17" s="14">
         <v>0</v>
@@ -11156,24 +11163,24 @@
         <v>48.68</v>
       </c>
       <c r="L17" s="16">
-        <v>3265125.53</v>
+        <v>593896</v>
       </c>
       <c r="M17" s="16">
-        <v>816281.38</v>
+        <v>148474</v>
       </c>
       <c r="N17" s="16">
-        <v>2248844.15</v>
+        <v>245422</v>
       </c>
       <c r="O17" s="16">
-        <v>10357004.87</v>
+        <v>1612520.74</v>
       </c>
       <c r="P17" s="16">
-        <v>5867753.65</v>
+        <v>-690609.45</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" s="23">
         <v>7</v>
@@ -11182,19 +11189,19 @@
         <v>4249245</v>
       </c>
       <c r="E18" s="23">
-        <v>66070</v>
+        <v>15443</v>
       </c>
       <c r="F18" s="23">
-        <v>44221</v>
+        <v>2206</v>
       </c>
       <c r="G18" s="23">
-        <v>24908</v>
+        <v>262</v>
       </c>
       <c r="H18" s="23">
-        <v>135199</v>
+        <v>17911</v>
       </c>
       <c r="I18" s="24">
-        <v>0.0318</v>
+        <v>0.0042</v>
       </c>
       <c r="J18" s="24">
         <v>0.125</v>
@@ -11203,24 +11210,24 @@
         <v>48.4</v>
       </c>
       <c r="L18" s="25">
-        <v>6544104.8</v>
+        <v>866892.4</v>
       </c>
       <c r="M18" s="25">
-        <v>1636026.2</v>
+        <v>216723.1</v>
       </c>
       <c r="N18" s="25">
-        <v>4708078.6</v>
+        <v>450169.3</v>
       </c>
       <c r="O18" s="25">
-        <v>16901109.66</v>
+        <v>2479413.14</v>
       </c>
       <c r="P18" s="25">
-        <v>10575832.25</v>
+        <v>-240440.15</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="21">
         <v>8</v>
@@ -11229,19 +11236,19 @@
         <v>4256327</v>
       </c>
       <c r="E19" s="21">
-        <v>81432</v>
+        <v>18387</v>
       </c>
       <c r="F19" s="21">
-        <v>78107</v>
+        <v>6128</v>
       </c>
       <c r="G19" s="21">
-        <v>38374</v>
+        <v>933</v>
       </c>
       <c r="H19" s="21">
-        <v>197913</v>
+        <v>25448</v>
       </c>
       <c r="I19" s="14">
-        <v>0.0465</v>
+        <v>0.006</v>
       </c>
       <c r="J19" s="14">
         <v>0.25</v>
@@ -11250,24 +11257,24 @@
         <v>48.13</v>
       </c>
       <c r="L19" s="16">
-        <v>9525354.779999999</v>
+        <v>1224812.24</v>
       </c>
       <c r="M19" s="16">
-        <v>2381338.69</v>
+        <v>306203.06</v>
       </c>
       <c r="N19" s="16">
-        <v>6944016.08</v>
+        <v>718609.1800000001</v>
       </c>
       <c r="O19" s="16">
-        <v>26426464.44</v>
+        <v>3704225.38</v>
       </c>
       <c r="P19" s="16">
-        <v>17519848.33</v>
+        <v>478169.03</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="23">
         <v>9</v>
@@ -11276,19 +11283,19 @@
         <v>4263421</v>
       </c>
       <c r="E20" s="23">
-        <v>97703</v>
+        <v>20372</v>
       </c>
       <c r="F20" s="23">
-        <v>100723</v>
+        <v>12222</v>
       </c>
       <c r="G20" s="23">
-        <v>55251</v>
+        <v>2303</v>
       </c>
       <c r="H20" s="23">
-        <v>253677</v>
+        <v>34897</v>
       </c>
       <c r="I20" s="24">
-        <v>0.0595</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="J20" s="24">
         <v>0.375</v>
@@ -11297,24 +11304,24 @@
         <v>47.85</v>
       </c>
       <c r="L20" s="25">
-        <v>12139586</v>
+        <v>1669821.45</v>
       </c>
       <c r="M20" s="25">
-        <v>3034896.5</v>
+        <v>417455.36</v>
       </c>
       <c r="N20" s="25">
-        <v>8904689.5</v>
+        <v>1052366.09</v>
       </c>
       <c r="O20" s="25">
-        <v>38566050.44</v>
+        <v>5374046.83</v>
       </c>
       <c r="P20" s="25">
-        <v>26424537.83</v>
+        <v>1530535.12</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C21" s="21">
         <v>10</v>
@@ -11323,19 +11330,19 @@
         <v>4270527</v>
       </c>
       <c r="E21" s="21">
-        <v>114027</v>
+        <v>21034</v>
       </c>
       <c r="F21" s="21">
-        <v>112306</v>
+        <v>21033</v>
       </c>
       <c r="G21" s="21">
-        <v>64482</v>
+        <v>4059</v>
       </c>
       <c r="H21" s="21">
-        <v>290815</v>
+        <v>46126</v>
       </c>
       <c r="I21" s="14">
-        <v>0.06809999999999999</v>
+        <v>0.0108</v>
       </c>
       <c r="J21" s="14">
         <v>0.5</v>
@@ -11344,24 +11351,24 @@
         <v>47.58</v>
       </c>
       <c r="L21" s="16">
-        <v>13836977.7</v>
+        <v>2194675.08</v>
       </c>
       <c r="M21" s="16">
-        <v>3459244.42</v>
+        <v>548668.77</v>
       </c>
       <c r="N21" s="16">
-        <v>10177733.27</v>
+        <v>1446006.31</v>
       </c>
       <c r="O21" s="16">
-        <v>52403028.14</v>
+        <v>7568721.91</v>
       </c>
       <c r="P21" s="16">
-        <v>36602271.1</v>
+        <v>2976541.43</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" s="22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C22" s="23">
         <v>11</v>
@@ -11370,19 +11377,19 @@
         <v>4277644</v>
       </c>
       <c r="E22" s="23">
-        <v>129547</v>
+        <v>19620</v>
       </c>
       <c r="F22" s="23">
-        <v>114279</v>
+        <v>32698</v>
       </c>
       <c r="G22" s="23">
-        <v>73258</v>
+        <v>6466</v>
       </c>
       <c r="H22" s="23">
-        <v>317084</v>
+        <v>58784</v>
       </c>
       <c r="I22" s="24">
-        <v>0.0741</v>
+        <v>0.0137</v>
       </c>
       <c r="J22" s="24">
         <v>0.625</v>
@@ -11391,24 +11398,24 @@
         <v>47.31</v>
       </c>
       <c r="L22" s="25">
-        <v>14999817.16</v>
+        <v>2781071.04</v>
       </c>
       <c r="M22" s="25">
-        <v>3749954.29</v>
+        <v>695267.76</v>
       </c>
       <c r="N22" s="25">
-        <v>11049862.87</v>
+        <v>1885803.28</v>
       </c>
       <c r="O22" s="25">
-        <v>67402845.3</v>
+        <v>10349792.95</v>
       </c>
       <c r="P22" s="25">
-        <v>47652133.97</v>
+        <v>4862344.71</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C23" s="21">
         <v>12</v>
@@ -11417,19 +11424,19 @@
         <v>4284774</v>
       </c>
       <c r="E23" s="21">
-        <v>143569</v>
+        <v>15702</v>
       </c>
       <c r="F23" s="21">
-        <v>121473</v>
+        <v>47105</v>
       </c>
       <c r="G23" s="21">
-        <v>81188</v>
+        <v>9551</v>
       </c>
       <c r="H23" s="21">
-        <v>346230</v>
+        <v>72358</v>
       </c>
       <c r="I23" s="14">
-        <v>0.0808</v>
+        <v>0.0169</v>
       </c>
       <c r="J23" s="14">
         <v>0.75</v>
@@ -11438,24 +11445,24 @@
         <v>47.03</v>
       </c>
       <c r="L23" s="16">
-        <v>16283543.13</v>
+        <v>3402996.74</v>
       </c>
       <c r="M23" s="16">
-        <v>4070885.78</v>
+        <v>850749.1899999999</v>
       </c>
       <c r="N23" s="16">
-        <v>12012657.35</v>
+        <v>2352247.56</v>
       </c>
       <c r="O23" s="16">
-        <v>83686388.43000001</v>
+        <v>13752789.69</v>
       </c>
       <c r="P23" s="16">
-        <v>59664791.32</v>
+        <v>7214592.27</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" s="22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" s="23">
         <v>13</v>
@@ -11464,19 +11471,19 @@
         <v>4291915</v>
       </c>
       <c r="E24" s="23">
-        <v>155676</v>
+        <v>18723</v>
       </c>
       <c r="F24" s="23">
-        <v>121675</v>
+        <v>56169</v>
       </c>
       <c r="G24" s="23">
-        <v>88034</v>
+        <v>11389</v>
       </c>
       <c r="H24" s="23">
-        <v>365385</v>
+        <v>86281</v>
       </c>
       <c r="I24" s="24">
-        <v>0.0851</v>
+        <v>0.0201</v>
       </c>
       <c r="J24" s="24">
         <v>0.75</v>
@@ -11485,24 +11492,24 @@
         <v>46.76</v>
       </c>
       <c r="L24" s="25">
-        <v>17084123.75</v>
+        <v>4034499.56</v>
       </c>
       <c r="M24" s="25">
-        <v>4271030.94</v>
+        <v>1008624.89</v>
       </c>
       <c r="N24" s="25">
-        <v>12613092.81</v>
+        <v>2825874.67</v>
       </c>
       <c r="O24" s="25">
-        <v>100770512.18</v>
+        <v>17787289.25</v>
       </c>
       <c r="P24" s="25">
-        <v>72277884.13</v>
+        <v>10040466.94</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C25" s="21">
         <v>14</v>
@@ -11511,19 +11518,19 @@
         <v>4299068</v>
       </c>
       <c r="E25" s="21">
-        <v>165736</v>
+        <v>21704</v>
       </c>
       <c r="F25" s="21">
-        <v>121878</v>
+        <v>65112</v>
       </c>
       <c r="G25" s="21">
-        <v>93723</v>
+        <v>13202</v>
       </c>
       <c r="H25" s="21">
-        <v>381337</v>
+        <v>100018</v>
       </c>
       <c r="I25" s="14">
-        <v>0.0887</v>
+        <v>0.0233</v>
       </c>
       <c r="J25" s="14">
         <v>0.75</v>
@@ -11532,24 +11539,24 @@
         <v>46.48</v>
       </c>
       <c r="L25" s="16">
-        <v>17725306.43</v>
+        <v>4648836.64</v>
       </c>
       <c r="M25" s="16">
-        <v>4431326.61</v>
+        <v>1162209.16</v>
       </c>
       <c r="N25" s="16">
-        <v>13093979.83</v>
+        <v>3286627.48</v>
       </c>
       <c r="O25" s="16">
-        <v>118495818.61</v>
+        <v>22436125.89</v>
       </c>
       <c r="P25" s="16">
-        <v>85371863.95999999</v>
+        <v>13327094.42</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C26" s="23">
         <v>15</v>
@@ -11558,19 +11565,19 @@
         <v>4306233</v>
       </c>
       <c r="E26" s="23">
-        <v>173842</v>
+        <v>24552</v>
       </c>
       <c r="F26" s="23">
-        <v>122081</v>
+        <v>73654</v>
       </c>
       <c r="G26" s="23">
-        <v>105630</v>
+        <v>14934</v>
       </c>
       <c r="H26" s="23">
-        <v>401553</v>
+        <v>113140</v>
       </c>
       <c r="I26" s="24">
-        <v>0.09320000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="J26" s="24">
         <v>0.75</v>
@@ -11579,24 +11586,24 @@
         <v>46.21</v>
       </c>
       <c r="L26" s="25">
-        <v>18554760.25</v>
+        <v>5228199.4</v>
       </c>
       <c r="M26" s="25">
-        <v>4638690.06</v>
+        <v>1307049.85</v>
       </c>
       <c r="N26" s="25">
-        <v>13716070.19</v>
+        <v>3721149.55</v>
       </c>
       <c r="O26" s="25">
-        <v>137050578.86</v>
+        <v>27664325.29</v>
       </c>
       <c r="P26" s="25">
-        <v>99087934.15000001</v>
+        <v>17048243.97</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C27" s="21">
         <v>16</v>
@@ -11605,19 +11612,19 @@
         <v>4313410</v>
       </c>
       <c r="E27" s="21">
-        <v>180221</v>
+        <v>27200</v>
       </c>
       <c r="F27" s="21">
-        <v>122285</v>
+        <v>81598</v>
       </c>
       <c r="G27" s="21">
-        <v>109506</v>
+        <v>16545</v>
       </c>
       <c r="H27" s="21">
-        <v>412012</v>
+        <v>125343</v>
       </c>
       <c r="I27" s="14">
-        <v>0.0955</v>
+        <v>0.0291</v>
       </c>
       <c r="J27" s="14">
         <v>0.75</v>
@@ -11626,24 +11633,24 @@
         <v>45.93</v>
       </c>
       <c r="L27" s="16">
-        <v>18924947.2</v>
+        <v>5757003.99</v>
       </c>
       <c r="M27" s="16">
-        <v>4731236.8</v>
+        <v>1439251</v>
       </c>
       <c r="N27" s="16">
-        <v>13993710.4</v>
+        <v>4117752.99</v>
       </c>
       <c r="O27" s="16">
-        <v>155975526.06</v>
+        <v>33421329.28</v>
       </c>
       <c r="P27" s="16">
-        <v>113081644.54</v>
+        <v>21165996.96</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C28" s="23">
         <v>17</v>
@@ -11652,19 +11659,19 @@
         <v>4320599</v>
       </c>
       <c r="E28" s="23">
-        <v>185161</v>
+        <v>29609</v>
       </c>
       <c r="F28" s="23">
-        <v>122489</v>
+        <v>88827</v>
       </c>
       <c r="G28" s="23">
-        <v>112508</v>
+        <v>18011</v>
       </c>
       <c r="H28" s="23">
-        <v>420158</v>
+        <v>136447</v>
       </c>
       <c r="I28" s="24">
-        <v>0.09719999999999999</v>
+        <v>0.0316</v>
       </c>
       <c r="J28" s="24">
         <v>0.75</v>
@@ -11673,24 +11680,24 @@
         <v>45.66</v>
       </c>
       <c r="L28" s="25">
-        <v>19183784.04</v>
+        <v>6230170.02</v>
       </c>
       <c r="M28" s="25">
-        <v>4795946.01</v>
+        <v>1557542.5</v>
       </c>
       <c r="N28" s="25">
-        <v>14187838.03</v>
+        <v>4472627.51</v>
       </c>
       <c r="O28" s="25">
-        <v>175159310.1</v>
+        <v>39651499.3</v>
       </c>
       <c r="P28" s="25">
-        <v>127269482.57</v>
+        <v>25638624.48</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C29" s="21">
         <v>18</v>
@@ -11699,19 +11706,19 @@
         <v>4327800</v>
       </c>
       <c r="E29" s="21">
-        <v>188950</v>
+        <v>31764</v>
       </c>
       <c r="F29" s="21">
-        <v>122693</v>
+        <v>95289</v>
       </c>
       <c r="G29" s="21">
-        <v>114810</v>
+        <v>19321</v>
       </c>
       <c r="H29" s="21">
-        <v>426453</v>
+        <v>146374</v>
       </c>
       <c r="I29" s="14">
-        <v>0.0985</v>
+        <v>0.0338</v>
       </c>
       <c r="J29" s="14">
         <v>0.75</v>
@@ -11720,24 +11727,24 @@
         <v>45.38</v>
       </c>
       <c r="L29" s="16">
-        <v>19354142.95</v>
+        <v>6642452.12</v>
       </c>
       <c r="M29" s="16">
-        <v>4838535.74</v>
+        <v>1660613.03</v>
       </c>
       <c r="N29" s="16">
-        <v>14315607.21</v>
+        <v>4781839.09</v>
       </c>
       <c r="O29" s="16">
-        <v>194513453.05</v>
+        <v>46293951.42</v>
       </c>
       <c r="P29" s="16">
-        <v>141585089.79</v>
+        <v>30420463.57</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C30" s="23">
         <v>19</v>
@@ -11746,19 +11753,19 @@
         <v>4335013</v>
       </c>
       <c r="E30" s="23">
-        <v>191844</v>
+        <v>33663</v>
       </c>
       <c r="F30" s="23">
-        <v>122897</v>
+        <v>100986</v>
       </c>
       <c r="G30" s="23">
-        <v>116569</v>
+        <v>20476</v>
       </c>
       <c r="H30" s="23">
-        <v>431310</v>
+        <v>155125</v>
       </c>
       <c r="I30" s="24">
-        <v>0.09950000000000001</v>
+        <v>0.0358</v>
       </c>
       <c r="J30" s="24">
         <v>0.75</v>
@@ -11767,24 +11774,24 @@
         <v>45.11</v>
       </c>
       <c r="L30" s="25">
-        <v>19456178.45</v>
+        <v>6997688.75</v>
       </c>
       <c r="M30" s="25">
-        <v>4864044.61</v>
+        <v>1749422.19</v>
       </c>
       <c r="N30" s="25">
-        <v>14392133.83</v>
+        <v>5048266.56</v>
       </c>
       <c r="O30" s="25">
-        <v>213969631.5</v>
+        <v>53291640.17</v>
       </c>
       <c r="P30" s="25">
-        <v>155977223.62</v>
+        <v>35468730.13</v>
       </c>
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C31" s="21">
         <v>20</v>
@@ -11793,19 +11800,19 @@
         <v>4342238</v>
       </c>
       <c r="E31" s="21">
-        <v>194058</v>
+        <v>35318</v>
       </c>
       <c r="F31" s="21">
-        <v>123102</v>
+        <v>105951</v>
       </c>
       <c r="G31" s="21">
-        <v>117914</v>
+        <v>21483</v>
       </c>
       <c r="H31" s="21">
-        <v>435074</v>
+        <v>162752</v>
       </c>
       <c r="I31" s="14">
-        <v>0.1002</v>
+        <v>0.0375</v>
       </c>
       <c r="J31" s="14">
         <v>0.75</v>
@@ -11814,24 +11821,24 @@
         <v>44.84</v>
       </c>
       <c r="L31" s="16">
-        <v>19506542.79</v>
+        <v>7297799.68</v>
       </c>
       <c r="M31" s="16">
-        <v>4876635.7</v>
+        <v>1824449.92</v>
       </c>
       <c r="N31" s="16">
-        <v>14429907.09</v>
+        <v>5273349.76</v>
       </c>
       <c r="O31" s="16">
-        <v>233476174.29</v>
+        <v>60589439.85</v>
       </c>
       <c r="P31" s="16">
-        <v>170407130.72</v>
+        <v>40742079.89</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C32" s="23">
         <v>21</v>
@@ -11840,19 +11847,19 @@
         <v>4349476</v>
       </c>
       <c r="E32" s="23">
-        <v>195765</v>
+        <v>36747</v>
       </c>
       <c r="F32" s="23">
-        <v>123307</v>
+        <v>110240</v>
       </c>
       <c r="G32" s="23">
-        <v>118951</v>
+        <v>22352</v>
       </c>
       <c r="H32" s="23">
-        <v>438023</v>
+        <v>169339</v>
       </c>
       <c r="I32" s="24">
-        <v>0.1007</v>
+        <v>0.0389</v>
       </c>
       <c r="J32" s="24">
         <v>0.75</v>
@@ -11861,24 +11868,24 @@
         <v>44.56</v>
       </c>
       <c r="L32" s="25">
-        <v>19518523.89</v>
+        <v>7545745.84</v>
       </c>
       <c r="M32" s="25">
-        <v>4879630.97</v>
+        <v>1886436.46</v>
       </c>
       <c r="N32" s="25">
-        <v>14438892.92</v>
+        <v>5459309.38</v>
       </c>
       <c r="O32" s="25">
-        <v>252994698.18</v>
+        <v>68135185.69</v>
       </c>
       <c r="P32" s="25">
-        <v>184846023.63</v>
+        <v>46201389.27</v>
       </c>
     </row>
     <row r="33" spans="2:16">
       <c r="B33" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C33" s="21">
         <v>22</v>
@@ -11887,19 +11894,19 @@
         <v>4356725</v>
       </c>
       <c r="E33" s="21">
-        <v>197096</v>
+        <v>37973</v>
       </c>
       <c r="F33" s="21">
-        <v>123513</v>
+        <v>113919</v>
       </c>
       <c r="G33" s="21">
-        <v>119760</v>
+        <v>23098</v>
       </c>
       <c r="H33" s="21">
-        <v>440369</v>
+        <v>174990</v>
       </c>
       <c r="I33" s="14">
-        <v>0.1011</v>
+        <v>0.0402</v>
       </c>
       <c r="J33" s="14">
         <v>0.75</v>
@@ -11908,24 +11915,24 @@
         <v>44.29</v>
       </c>
       <c r="L33" s="16">
-        <v>19502181.53</v>
+        <v>7750307.1</v>
       </c>
       <c r="M33" s="16">
-        <v>4875545.38</v>
+        <v>1937576.77</v>
       </c>
       <c r="N33" s="16">
-        <v>14426636.15</v>
+        <v>5612730.32</v>
       </c>
       <c r="O33" s="16">
-        <v>272496879.71</v>
+        <v>75885492.79000001</v>
       </c>
       <c r="P33" s="16">
-        <v>199272659.78</v>
+        <v>51814119.59</v>
       </c>
     </row>
     <row r="34" spans="2:16">
       <c r="B34" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C34" s="23">
         <v>23</v>
@@ -11934,19 +11941,19 @@
         <v>4363986</v>
       </c>
       <c r="E34" s="23">
-        <v>198152</v>
+        <v>39020</v>
       </c>
       <c r="F34" s="23">
-        <v>123719</v>
+        <v>117058</v>
       </c>
       <c r="G34" s="23">
-        <v>120402</v>
+        <v>23735</v>
       </c>
       <c r="H34" s="23">
-        <v>442273</v>
+        <v>179813</v>
       </c>
       <c r="I34" s="24">
-        <v>0.1013</v>
+        <v>0.0412</v>
       </c>
       <c r="J34" s="24">
         <v>0.75</v>
@@ -11955,24 +11962,24 @@
         <v>44.01</v>
       </c>
       <c r="L34" s="25">
-        <v>19465098.14</v>
+        <v>7913570.13</v>
       </c>
       <c r="M34" s="25">
-        <v>4866274.53</v>
+        <v>1978392.53</v>
       </c>
       <c r="N34" s="25">
-        <v>14398823.6</v>
+        <v>5735177.6</v>
       </c>
       <c r="O34" s="25">
-        <v>291961977.85</v>
+        <v>83799062.92</v>
       </c>
       <c r="P34" s="25">
-        <v>213671483.39</v>
+        <v>57549297.19</v>
       </c>
     </row>
     <row r="35" spans="2:16">
       <c r="B35" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C35" s="21">
         <v>24</v>
@@ -11981,19 +11988,19 @@
         <v>4371259</v>
       </c>
       <c r="E35" s="21">
-        <v>199008</v>
+        <v>39910</v>
       </c>
       <c r="F35" s="21">
-        <v>123925</v>
+        <v>119730</v>
       </c>
       <c r="G35" s="21">
-        <v>120922</v>
+        <v>24276</v>
       </c>
       <c r="H35" s="21">
-        <v>443855</v>
+        <v>183916</v>
       </c>
       <c r="I35" s="14">
-        <v>0.1015</v>
+        <v>0.0421</v>
       </c>
       <c r="J35" s="14">
         <v>0.75</v>
@@ -12002,24 +12009,24 @@
         <v>43.74</v>
       </c>
       <c r="L35" s="16">
-        <v>19412886.14</v>
+        <v>8044485.84</v>
       </c>
       <c r="M35" s="16">
-        <v>4853221.53</v>
+        <v>2011121.46</v>
       </c>
       <c r="N35" s="16">
-        <v>14359664.6</v>
+        <v>5833364.38</v>
       </c>
       <c r="O35" s="16">
-        <v>311374863.99</v>
+        <v>91843548.76000001</v>
       </c>
       <c r="P35" s="16">
-        <v>228031147.99</v>
+        <v>63382661.57</v>
       </c>
     </row>
     <row r="36" spans="2:16">
       <c r="B36" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C36" s="23">
         <v>25</v>
@@ -12028,19 +12035,19 @@
         <v>4378545</v>
       </c>
       <c r="E36" s="23">
-        <v>199719</v>
+        <v>40666</v>
       </c>
       <c r="F36" s="23">
-        <v>124131</v>
+        <v>121996</v>
       </c>
       <c r="G36" s="23">
-        <v>121354</v>
+        <v>24736</v>
       </c>
       <c r="H36" s="23">
-        <v>445204</v>
+        <v>187398</v>
       </c>
       <c r="I36" s="24">
-        <v>0.1017</v>
+        <v>0.0428</v>
       </c>
       <c r="J36" s="24">
         <v>0.75</v>
@@ -12049,24 +12056,24 @@
         <v>43.46</v>
       </c>
       <c r="L36" s="25">
-        <v>19349678.85</v>
+        <v>8144317.08</v>
       </c>
       <c r="M36" s="25">
-        <v>4837419.71</v>
+        <v>2036079.27</v>
       </c>
       <c r="N36" s="25">
-        <v>14312259.14</v>
+        <v>5908237.81</v>
       </c>
       <c r="O36" s="25">
-        <v>330724542.84</v>
+        <v>99987865.84</v>
       </c>
       <c r="P36" s="25">
-        <v>242343407.13</v>
+        <v>69290899.38</v>
       </c>
     </row>
     <row r="37" spans="2:16">
       <c r="B37" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C37" s="21">
         <v>26</v>
@@ -12075,19 +12082,19 @@
         <v>4385842</v>
       </c>
       <c r="E37" s="21">
-        <v>200324</v>
+        <v>41307</v>
       </c>
       <c r="F37" s="21">
-        <v>124338</v>
+        <v>123919</v>
       </c>
       <c r="G37" s="21">
-        <v>121721</v>
+        <v>25126</v>
       </c>
       <c r="H37" s="21">
-        <v>446383</v>
+        <v>190352</v>
       </c>
       <c r="I37" s="14">
-        <v>0.1018</v>
+        <v>0.0434</v>
       </c>
       <c r="J37" s="14">
         <v>0.75</v>
@@ -12096,24 +12103,24 @@
         <v>43.19</v>
       </c>
       <c r="L37" s="16">
-        <v>19278389</v>
+        <v>8221302.88</v>
       </c>
       <c r="M37" s="16">
-        <v>4819597.25</v>
+        <v>2055325.72</v>
       </c>
       <c r="N37" s="16">
-        <v>14258791.75</v>
+        <v>5965977.16</v>
       </c>
       <c r="O37" s="16">
-        <v>350002931.84</v>
+        <v>108209168.72</v>
       </c>
       <c r="P37" s="16">
-        <v>256602198.88</v>
+        <v>75256876.54000001</v>
       </c>
     </row>
     <row r="38" spans="2:16">
       <c r="B38" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C38" s="23">
         <v>27</v>
@@ -12122,19 +12129,19 @@
         <v>4393152</v>
       </c>
       <c r="E38" s="23">
-        <v>200854</v>
+        <v>41851</v>
       </c>
       <c r="F38" s="23">
-        <v>124545</v>
+        <v>125551</v>
       </c>
       <c r="G38" s="23">
-        <v>122043</v>
+        <v>25457</v>
       </c>
       <c r="H38" s="23">
-        <v>447442</v>
+        <v>192859</v>
       </c>
       <c r="I38" s="24">
-        <v>0.1018</v>
+        <v>0.0439</v>
       </c>
       <c r="J38" s="24">
         <v>0.75</v>
@@ -12143,24 +12150,24 @@
         <v>42.91</v>
       </c>
       <c r="L38" s="25">
-        <v>19201302.27</v>
+        <v>8275579.69</v>
       </c>
       <c r="M38" s="25">
-        <v>4800325.57</v>
+        <v>2068894.92</v>
       </c>
       <c r="N38" s="25">
-        <v>14200976.7</v>
+        <v>6006684.77</v>
       </c>
       <c r="O38" s="25">
-        <v>369204234.11</v>
+        <v>116484748.41</v>
       </c>
       <c r="P38" s="25">
-        <v>270803175.58</v>
+        <v>81263561.31</v>
       </c>
     </row>
     <row r="39" spans="2:16">
       <c r="B39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C39" s="21">
         <v>28</v>
@@ -12169,19 +12176,19 @@
         <v>4400474</v>
       </c>
       <c r="E39" s="21">
-        <v>201330</v>
+        <v>42314</v>
       </c>
       <c r="F39" s="21">
-        <v>124753</v>
+        <v>126940</v>
       </c>
       <c r="G39" s="21">
-        <v>122333</v>
+        <v>25739</v>
       </c>
       <c r="H39" s="21">
-        <v>448416</v>
+        <v>194993</v>
       </c>
       <c r="I39" s="14">
-        <v>0.1019</v>
+        <v>0.0443</v>
       </c>
       <c r="J39" s="14">
         <v>0.75</v>
@@ -12190,24 +12197,24 @@
         <v>42.64</v>
       </c>
       <c r="L39" s="16">
-        <v>19120009.82</v>
+        <v>8314501.52</v>
       </c>
       <c r="M39" s="16">
-        <v>4780002.46</v>
+        <v>2078625.38</v>
       </c>
       <c r="N39" s="16">
-        <v>14140007.37</v>
+        <v>6035876.14</v>
       </c>
       <c r="O39" s="16">
-        <v>388324243.93</v>
+        <v>124799249.93</v>
       </c>
       <c r="P39" s="16">
-        <v>284943182.95</v>
+        <v>87299437.45</v>
       </c>
     </row>
     <row r="40" spans="2:16">
       <c r="B40" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C40" s="23">
         <v>29</v>
@@ -12216,19 +12223,19 @@
         <v>4407808</v>
       </c>
       <c r="E40" s="23">
-        <v>201767</v>
+        <v>42709</v>
       </c>
       <c r="F40" s="23">
-        <v>124961</v>
+        <v>128125</v>
       </c>
       <c r="G40" s="23">
-        <v>122598</v>
+        <v>25979</v>
       </c>
       <c r="H40" s="23">
-        <v>449326</v>
+        <v>196813</v>
       </c>
       <c r="I40" s="24">
-        <v>0.1019</v>
+        <v>0.0447</v>
       </c>
       <c r="J40" s="24">
         <v>0.75</v>
@@ -12237,24 +12244,24 @@
         <v>42.36</v>
       </c>
       <c r="L40" s="25">
-        <v>19035471.33</v>
+        <v>8336998.68</v>
       </c>
       <c r="M40" s="25">
-        <v>4758867.83</v>
+        <v>2084249.67</v>
       </c>
       <c r="N40" s="25">
-        <v>14076603.5</v>
+        <v>6052749.01</v>
       </c>
       <c r="O40" s="25">
-        <v>407359715.26</v>
+        <v>133136248.61</v>
       </c>
       <c r="P40" s="25">
-        <v>299019786.44</v>
+        <v>93352186.45999999</v>
       </c>
     </row>
     <row r="41" spans="2:16">
       <c r="B41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C41" s="21">
         <v>30</v>
@@ -12263,19 +12270,19 @@
         <v>4415154</v>
       </c>
       <c r="E41" s="21">
-        <v>202176</v>
+        <v>43048</v>
       </c>
       <c r="F41" s="21">
-        <v>125169</v>
+        <v>129141</v>
       </c>
       <c r="G41" s="21">
-        <v>122847</v>
+        <v>26185</v>
       </c>
       <c r="H41" s="21">
-        <v>450192</v>
+        <v>198374</v>
       </c>
       <c r="I41" s="14">
-        <v>0.102</v>
+        <v>0.0449</v>
       </c>
       <c r="J41" s="14">
         <v>0.75</v>
@@ -12284,24 +12291,24 @@
         <v>42.09</v>
       </c>
       <c r="L41" s="16">
-        <v>18948581.28</v>
+        <v>8349561.66</v>
       </c>
       <c r="M41" s="16">
-        <v>4737145.32</v>
+        <v>2087390.42</v>
       </c>
       <c r="N41" s="16">
-        <v>14011435.96</v>
+        <v>6062171.25</v>
       </c>
       <c r="O41" s="16">
-        <v>426308296.54</v>
+        <v>141485810.27</v>
       </c>
       <c r="P41" s="16">
-        <v>313031222.4</v>
+        <v>99414357.7</v>
       </c>
     </row>
     <row r="42" spans="2:16">
       <c r="B42" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C42" s="23">
         <v>31</v>
@@ -12310,19 +12317,19 @@
         <v>4422513</v>
       </c>
       <c r="E42" s="23">
-        <v>202566</v>
+        <v>43339</v>
       </c>
       <c r="F42" s="23">
-        <v>125378</v>
+        <v>130017</v>
       </c>
       <c r="G42" s="23">
-        <v>123084</v>
+        <v>26362</v>
       </c>
       <c r="H42" s="23">
-        <v>451028</v>
+        <v>199718</v>
       </c>
       <c r="I42" s="24">
-        <v>0.102</v>
+        <v>0.0452</v>
       </c>
       <c r="J42" s="24">
         <v>0.75</v>
@@ -12331,24 +12338,24 @@
         <v>41.82</v>
       </c>
       <c r="L42" s="25">
-        <v>18859961.33</v>
+        <v>8352206.76</v>
       </c>
       <c r="M42" s="25">
-        <v>4714990.33</v>
+        <v>2088051.69</v>
       </c>
       <c r="N42" s="25">
-        <v>13944971</v>
+        <v>6064155.07</v>
       </c>
       <c r="O42" s="25">
-        <v>445168257.87</v>
+        <v>149838017.03</v>
       </c>
       <c r="P42" s="25">
-        <v>326976193.4</v>
+        <v>105478512.77</v>
       </c>
     </row>
     <row r="43" spans="2:16">
       <c r="B43" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C43" s="21">
         <v>32</v>
@@ -12357,19 +12364,19 @@
         <v>4429884</v>
       </c>
       <c r="E43" s="21">
-        <v>202941</v>
+        <v>43593</v>
       </c>
       <c r="F43" s="21">
-        <v>125587</v>
+        <v>130776</v>
       </c>
       <c r="G43" s="21">
-        <v>123312</v>
+        <v>26516</v>
       </c>
       <c r="H43" s="21">
-        <v>451840</v>
+        <v>200885</v>
       </c>
       <c r="I43" s="14">
-        <v>0.102</v>
+        <v>0.0453</v>
       </c>
       <c r="J43" s="14">
         <v>0.75</v>
@@ -12378,24 +12385,24 @@
         <v>41.54</v>
       </c>
       <c r="L43" s="16">
-        <v>18769885.44</v>
+        <v>8344762.9</v>
       </c>
       <c r="M43" s="16">
-        <v>4692471.36</v>
+        <v>2086190.72</v>
       </c>
       <c r="N43" s="16">
-        <v>13877414.08</v>
+        <v>6058572.17</v>
       </c>
       <c r="O43" s="16">
-        <v>463938143.31</v>
+        <v>158182779.93</v>
       </c>
       <c r="P43" s="16">
-        <v>340853607.48</v>
+        <v>111537084.95</v>
       </c>
     </row>
     <row r="44" spans="2:16">
       <c r="B44" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C44" s="23">
         <v>33</v>
@@ -12404,19 +12411,19 @@
         <v>4437267</v>
       </c>
       <c r="E44" s="23">
-        <v>203306</v>
+        <v>43814</v>
       </c>
       <c r="F44" s="23">
-        <v>125796</v>
+        <v>131440</v>
       </c>
       <c r="G44" s="23">
-        <v>123533</v>
+        <v>26651</v>
       </c>
       <c r="H44" s="23">
-        <v>452635</v>
+        <v>201905</v>
       </c>
       <c r="I44" s="24">
-        <v>0.102</v>
+        <v>0.0455</v>
       </c>
       <c r="J44" s="24">
         <v>0.75</v>
@@ -12425,24 +12432,24 @@
         <v>41.27</v>
       </c>
       <c r="L44" s="25">
-        <v>18678662.23</v>
+        <v>8332619.35</v>
       </c>
       <c r="M44" s="25">
-        <v>4669665.56</v>
+        <v>2083154.84</v>
       </c>
       <c r="N44" s="25">
-        <v>13808996.67</v>
+        <v>6049464.51</v>
       </c>
       <c r="O44" s="25">
-        <v>482616805.54</v>
+        <v>166515399.28</v>
       </c>
       <c r="P44" s="25">
-        <v>354662604.16</v>
+        <v>117586549.46</v>
       </c>
     </row>
     <row r="45" spans="2:16">
       <c r="B45" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C45" s="21">
         <v>34</v>
@@ -12451,19 +12458,19 @@
         <v>4444662</v>
       </c>
       <c r="E45" s="21">
-        <v>203664</v>
+        <v>44009</v>
       </c>
       <c r="F45" s="21">
-        <v>126006</v>
+        <v>132025</v>
       </c>
       <c r="G45" s="21">
-        <v>123751</v>
+        <v>26770</v>
       </c>
       <c r="H45" s="21">
-        <v>453421</v>
+        <v>202804</v>
       </c>
       <c r="I45" s="14">
-        <v>0.102</v>
+        <v>0.0456</v>
       </c>
       <c r="J45" s="14">
         <v>0.75</v>
@@ -12472,24 +12479,24 @@
         <v>40.99</v>
       </c>
       <c r="L45" s="16">
-        <v>18586633.63</v>
+        <v>8312935.96</v>
       </c>
       <c r="M45" s="16">
-        <v>4646658.41</v>
+        <v>2078233.99</v>
       </c>
       <c r="N45" s="16">
-        <v>13739975.22</v>
+        <v>6034701.97</v>
       </c>
       <c r="O45" s="16">
-        <v>501203439.17</v>
+        <v>174828335.24</v>
       </c>
       <c r="P45" s="16">
-        <v>368402579.38</v>
+        <v>123621251.43</v>
       </c>
     </row>
     <row r="46" spans="2:16">
       <c r="B46" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C46" s="23">
         <v>35</v>
@@ -12498,19 +12505,19 @@
         <v>4452070</v>
       </c>
       <c r="E46" s="23">
-        <v>204018</v>
+        <v>44182</v>
       </c>
       <c r="F46" s="23">
-        <v>126216</v>
+        <v>132546</v>
       </c>
       <c r="G46" s="23">
-        <v>123966</v>
+        <v>26875</v>
       </c>
       <c r="H46" s="23">
-        <v>454200</v>
+        <v>203603</v>
       </c>
       <c r="I46" s="24">
-        <v>0.102</v>
+        <v>0.0457</v>
       </c>
       <c r="J46" s="24">
         <v>0.75</v>
@@ -12519,24 +12526,24 @@
         <v>40.72</v>
       </c>
       <c r="L46" s="25">
-        <v>18493888.5</v>
+        <v>8290714.16</v>
       </c>
       <c r="M46" s="25">
-        <v>4623472.13</v>
+        <v>2072678.54</v>
       </c>
       <c r="N46" s="25">
-        <v>13670416.38</v>
+        <v>6018035.62</v>
       </c>
       <c r="O46" s="25">
-        <v>519697327.67</v>
+        <v>183119049.4</v>
       </c>
       <c r="P46" s="25">
-        <v>382072995.75</v>
+        <v>129639287.05</v>
       </c>
     </row>
     <row r="47" spans="2:16">
       <c r="B47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C47" s="21">
         <v>36</v>
@@ -12545,19 +12552,19 @@
         <v>4459490</v>
       </c>
       <c r="E47" s="21">
-        <v>204368</v>
+        <v>44338</v>
       </c>
       <c r="F47" s="21">
-        <v>126426</v>
+        <v>133013</v>
       </c>
       <c r="G47" s="21">
-        <v>124179</v>
+        <v>26970</v>
       </c>
       <c r="H47" s="21">
-        <v>454973</v>
+        <v>204321</v>
       </c>
       <c r="I47" s="14">
-        <v>0.102</v>
+        <v>0.0458</v>
       </c>
       <c r="J47" s="14">
         <v>0.75</v>
@@ -12566,24 +12573,24 @@
         <v>40.44</v>
       </c>
       <c r="L47" s="16">
-        <v>18400473.04</v>
+        <v>8262741.24</v>
       </c>
       <c r="M47" s="16">
-        <v>4600118.26</v>
+        <v>2065685.31</v>
       </c>
       <c r="N47" s="16">
-        <v>13600354.78</v>
+        <v>5997055.93</v>
       </c>
       <c r="O47" s="16">
-        <v>538097800.71</v>
+        <v>191381790.64</v>
       </c>
       <c r="P47" s="16">
-        <v>395673350.53</v>
+        <v>135636342.98</v>
       </c>
     </row>
     <row r="48" spans="2:16">
       <c r="B48" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C48" s="23">
         <v>37</v>
@@ -12592,19 +12599,19 @@
         <v>4466923</v>
       </c>
       <c r="E48" s="23">
-        <v>204715</v>
+        <v>44479</v>
       </c>
       <c r="F48" s="23">
-        <v>126637</v>
+        <v>133437</v>
       </c>
       <c r="G48" s="23">
-        <v>124389</v>
+        <v>27056</v>
       </c>
       <c r="H48" s="23">
-        <v>455741</v>
+        <v>204972</v>
       </c>
       <c r="I48" s="24">
-        <v>0.102</v>
+        <v>0.0459</v>
       </c>
       <c r="J48" s="24">
         <v>0.75</v>
@@ -12613,24 +12620,24 @@
         <v>40.17</v>
       </c>
       <c r="L48" s="25">
-        <v>18306432.36</v>
+        <v>8233725.24</v>
       </c>
       <c r="M48" s="25">
-        <v>4576608.09</v>
+        <v>2058431.31</v>
       </c>
       <c r="N48" s="25">
-        <v>13529824.27</v>
+        <v>5975293.93</v>
       </c>
       <c r="O48" s="25">
-        <v>556404233.0700001</v>
+        <v>199615515.88</v>
       </c>
       <c r="P48" s="25">
-        <v>409203174.8</v>
+        <v>141611636.91</v>
       </c>
     </row>
     <row r="49" spans="2:16">
       <c r="B49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C49" s="21">
         <v>38</v>
@@ -12639,19 +12646,19 @@
         <v>4474368</v>
       </c>
       <c r="E49" s="21">
-        <v>205062</v>
+        <v>44609</v>
       </c>
       <c r="F49" s="21">
-        <v>126848</v>
+        <v>133825</v>
       </c>
       <c r="G49" s="21">
-        <v>124600</v>
+        <v>27134</v>
       </c>
       <c r="H49" s="21">
-        <v>456510</v>
+        <v>205568</v>
       </c>
       <c r="I49" s="14">
-        <v>0.102</v>
+        <v>0.0459</v>
       </c>
       <c r="J49" s="14">
         <v>0.75</v>
@@ -12660,24 +12667,24 @@
         <v>39.89</v>
       </c>
       <c r="L49" s="16">
-        <v>18212009.94</v>
+        <v>8200107.52</v>
       </c>
       <c r="M49" s="16">
-        <v>4553002.49</v>
+        <v>2050026.88</v>
       </c>
       <c r="N49" s="16">
-        <v>13459007.46</v>
+        <v>5950080.64</v>
       </c>
       <c r="O49" s="16">
-        <v>574616243.01</v>
+        <v>207815623.4</v>
       </c>
       <c r="P49" s="16">
-        <v>422662182.26</v>
+        <v>147561717.55</v>
       </c>
     </row>
     <row r="50" spans="2:16">
       <c r="B50" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C50" s="23">
         <v>39</v>
@@ -12686,19 +12693,19 @@
         <v>4481825</v>
       </c>
       <c r="E50" s="23">
-        <v>205407</v>
+        <v>44728</v>
       </c>
       <c r="F50" s="23">
-        <v>127059</v>
+        <v>134184</v>
       </c>
       <c r="G50" s="23">
-        <v>124810</v>
+        <v>27207</v>
       </c>
       <c r="H50" s="23">
-        <v>457276</v>
+        <v>206119</v>
       </c>
       <c r="I50" s="24">
-        <v>0.102</v>
+        <v>0.046</v>
       </c>
       <c r="J50" s="24">
         <v>0.75</v>
@@ -12707,24 +12714,24 @@
         <v>39.62</v>
       </c>
       <c r="L50" s="25">
-        <v>18117046.48</v>
+        <v>8166434.78</v>
       </c>
       <c r="M50" s="25">
-        <v>4529261.62</v>
+        <v>2041608.69</v>
       </c>
       <c r="N50" s="25">
-        <v>13387784.86</v>
+        <v>5924826.08</v>
       </c>
       <c r="O50" s="25">
-        <v>592733289.49</v>
+        <v>215982058.18</v>
       </c>
       <c r="P50" s="25">
-        <v>436049967.12</v>
+        <v>153486543.64</v>
       </c>
     </row>
     <row r="51" spans="2:16">
       <c r="B51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C51" s="21">
         <v>40</v>
@@ -12733,19 +12740,19 @@
         <v>4489295</v>
       </c>
       <c r="E51" s="21">
-        <v>205752</v>
+        <v>44840</v>
       </c>
       <c r="F51" s="21">
-        <v>127271</v>
+        <v>134519</v>
       </c>
       <c r="G51" s="21">
-        <v>125020</v>
+        <v>27275</v>
       </c>
       <c r="H51" s="21">
-        <v>458043</v>
+        <v>206634</v>
       </c>
       <c r="I51" s="14">
-        <v>0.102</v>
+        <v>0.046</v>
       </c>
       <c r="J51" s="14">
         <v>0.75</v>
@@ -12754,24 +12761,24 @@
         <v>39.35</v>
       </c>
       <c r="L51" s="16">
-        <v>18021701.84</v>
+        <v>8131047.9</v>
       </c>
       <c r="M51" s="16">
-        <v>4505425.46</v>
+        <v>2032761.98</v>
       </c>
       <c r="N51" s="16">
-        <v>13316276.38</v>
+        <v>5898285.93</v>
       </c>
       <c r="O51" s="16">
-        <v>610754991.33</v>
+        <v>224113106.08</v>
       </c>
       <c r="P51" s="16">
-        <v>449366243.5</v>
+        <v>159384829.56</v>
       </c>
     </row>
     <row r="52" spans="2:16">
       <c r="B52" s="22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C52" s="23">
         <v>41</v>
@@ -12780,19 +12787,19 @@
         <v>4496777</v>
       </c>
       <c r="E52" s="23">
-        <v>206097</v>
+        <v>44945</v>
       </c>
       <c r="F52" s="23">
-        <v>127483</v>
+        <v>134835</v>
       </c>
       <c r="G52" s="23">
-        <v>125229</v>
+        <v>27339</v>
       </c>
       <c r="H52" s="23">
-        <v>458809</v>
+        <v>207119</v>
       </c>
       <c r="I52" s="24">
-        <v>0.102</v>
+        <v>0.0461</v>
       </c>
       <c r="J52" s="24">
         <v>0.75</v>
@@ -12801,24 +12808,24 @@
         <v>39.07</v>
       </c>
       <c r="L52" s="25">
-        <v>17925897.03</v>
+        <v>8092139.33</v>
       </c>
       <c r="M52" s="25">
-        <v>4481474.26</v>
+        <v>2023034.83</v>
       </c>
       <c r="N52" s="25">
-        <v>13244422.78</v>
+        <v>5869104.5</v>
       </c>
       <c r="O52" s="25">
-        <v>628680888.36</v>
+        <v>232205245.41</v>
       </c>
       <c r="P52" s="25">
-        <v>462610666.27</v>
+        <v>165253934.06</v>
       </c>
     </row>
     <row r="53" spans="2:16">
       <c r="B53" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C53" s="21">
         <v>42</v>
@@ -12827,19 +12834,19 @@
         <v>4504271</v>
       </c>
       <c r="E53" s="21">
-        <v>206442</v>
+        <v>45045</v>
       </c>
       <c r="F53" s="21">
-        <v>127696</v>
+        <v>135134</v>
       </c>
       <c r="G53" s="21">
-        <v>125439</v>
+        <v>27400</v>
       </c>
       <c r="H53" s="21">
-        <v>459577</v>
+        <v>207579</v>
       </c>
       <c r="I53" s="14">
-        <v>0.102</v>
+        <v>0.0461</v>
       </c>
       <c r="J53" s="14">
         <v>0.75</v>
@@ -12848,24 +12855,24 @@
         <v>38.8</v>
       </c>
       <c r="L53" s="16">
-        <v>17829749.29</v>
+        <v>8054065.2</v>
       </c>
       <c r="M53" s="16">
-        <v>4457437.32</v>
+        <v>2013516.3</v>
       </c>
       <c r="N53" s="16">
-        <v>13172311.97</v>
+        <v>5840548.9</v>
       </c>
       <c r="O53" s="16">
-        <v>646510637.65</v>
+        <v>240259310.61</v>
       </c>
       <c r="P53" s="16">
-        <v>475782978.24</v>
+        <v>171094482.96</v>
       </c>
     </row>
     <row r="54" spans="2:16">
       <c r="B54" s="22" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C54" s="23">
         <v>43</v>
@@ -12874,19 +12881,19 @@
         <v>4511779</v>
       </c>
       <c r="E54" s="23">
-        <v>206787</v>
+        <v>45141</v>
       </c>
       <c r="F54" s="23">
-        <v>127908</v>
+        <v>135420</v>
       </c>
       <c r="G54" s="23">
-        <v>125648</v>
+        <v>27458</v>
       </c>
       <c r="H54" s="23">
-        <v>460343</v>
+        <v>208019</v>
       </c>
       <c r="I54" s="24">
-        <v>0.102</v>
+        <v>0.0461</v>
       </c>
       <c r="J54" s="24">
         <v>0.75</v>
@@ -12895,24 +12902,24 @@
         <v>38.52</v>
       </c>
       <c r="L54" s="25">
-        <v>17733102.87</v>
+        <v>8012891.88</v>
       </c>
       <c r="M54" s="25">
-        <v>4433275.72</v>
+        <v>2003222.97</v>
       </c>
       <c r="N54" s="25">
-        <v>13099827.16</v>
+        <v>5809668.91</v>
       </c>
       <c r="O54" s="25">
-        <v>664243740.53</v>
+        <v>248272202.49</v>
       </c>
       <c r="P54" s="25">
-        <v>488882805.4</v>
+        <v>176904151.87</v>
       </c>
     </row>
     <row r="55" spans="2:16">
       <c r="B55" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C55" s="21">
         <v>44</v>
@@ -12921,19 +12928,19 @@
         <v>4519298</v>
       </c>
       <c r="E55" s="21">
-        <v>207132</v>
+        <v>45233</v>
       </c>
       <c r="F55" s="21">
-        <v>128122</v>
+        <v>135696</v>
       </c>
       <c r="G55" s="21">
-        <v>125858</v>
+        <v>27514</v>
       </c>
       <c r="H55" s="21">
-        <v>461112</v>
+        <v>208443</v>
       </c>
       <c r="I55" s="14">
-        <v>0.102</v>
+        <v>0.0461</v>
       </c>
       <c r="J55" s="14">
         <v>0.75</v>
@@ -12942,24 +12949,24 @@
         <v>38.25</v>
       </c>
       <c r="L55" s="16">
-        <v>17636150.66</v>
+        <v>7972944.75</v>
       </c>
       <c r="M55" s="16">
-        <v>4409037.67</v>
+        <v>1993236.19</v>
       </c>
       <c r="N55" s="16">
-        <v>13027113</v>
+        <v>5779708.56</v>
       </c>
       <c r="O55" s="16">
-        <v>681879891.1900001</v>
+        <v>256245147.24</v>
       </c>
       <c r="P55" s="16">
-        <v>501909918.39</v>
+        <v>182683860.43</v>
       </c>
     </row>
     <row r="56" spans="2:16">
       <c r="B56" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C56" s="23">
         <v>45</v>
@@ -12968,19 +12975,19 @@
         <v>4526830</v>
       </c>
       <c r="E56" s="23">
-        <v>207478</v>
+        <v>45322</v>
       </c>
       <c r="F56" s="23">
-        <v>128335</v>
+        <v>135964</v>
       </c>
       <c r="G56" s="23">
-        <v>126068</v>
+        <v>27568</v>
       </c>
       <c r="H56" s="23">
-        <v>461881</v>
+        <v>208854</v>
       </c>
       <c r="I56" s="24">
-        <v>0.102</v>
+        <v>0.0461</v>
       </c>
       <c r="J56" s="24">
         <v>0.75</v>
@@ -12989,24 +12996,24 @@
         <v>37.97</v>
       </c>
       <c r="L56" s="25">
-        <v>17538776.27</v>
+        <v>7930186.38</v>
       </c>
       <c r="M56" s="25">
-        <v>4384694.07</v>
+        <v>1982546.59</v>
       </c>
       <c r="N56" s="25">
-        <v>12954082.2</v>
+        <v>5747639.79</v>
       </c>
       <c r="O56" s="25">
-        <v>699418667.46</v>
+        <v>264175333.62</v>
       </c>
       <c r="P56" s="25">
-        <v>514864000.6</v>
+        <v>188431500.22</v>
       </c>
     </row>
     <row r="57" spans="2:16">
       <c r="B57" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C57" s="21">
         <v>46</v>
@@ -13015,19 +13022,19 @@
         <v>4534375</v>
       </c>
       <c r="E57" s="21">
-        <v>207824</v>
+        <v>45409</v>
       </c>
       <c r="F57" s="21">
-        <v>128549</v>
+        <v>136224</v>
       </c>
       <c r="G57" s="21">
-        <v>126279</v>
+        <v>27621</v>
       </c>
       <c r="H57" s="21">
-        <v>462652</v>
+        <v>209254</v>
       </c>
       <c r="I57" s="14">
-        <v>0.102</v>
+        <v>0.0461</v>
       </c>
       <c r="J57" s="14">
         <v>0.75</v>
@@ -13036,24 +13043,24 @@
         <v>37.7</v>
       </c>
       <c r="L57" s="16">
-        <v>17441055.1</v>
+        <v>7888875.8</v>
       </c>
       <c r="M57" s="16">
-        <v>4360263.77</v>
+        <v>1972218.95</v>
       </c>
       <c r="N57" s="16">
-        <v>12880791.32</v>
+        <v>5716656.85</v>
       </c>
       <c r="O57" s="16">
-        <v>716859722.5599999</v>
+        <v>272064209.42</v>
       </c>
       <c r="P57" s="16">
-        <v>527744791.92</v>
+        <v>194148157.07</v>
       </c>
     </row>
     <row r="58" spans="2:16">
       <c r="B58" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C58" s="23">
         <v>47</v>
@@ -13062,19 +13069,19 @@
         <v>4541932</v>
       </c>
       <c r="E58" s="23">
-        <v>208171</v>
+        <v>45493</v>
       </c>
       <c r="F58" s="23">
-        <v>128763</v>
+        <v>136479</v>
       </c>
       <c r="G58" s="23">
-        <v>126489</v>
+        <v>27673</v>
       </c>
       <c r="H58" s="23">
-        <v>463423</v>
+        <v>209645</v>
       </c>
       <c r="I58" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J58" s="24">
         <v>0.75</v>
@@ -13083,24 +13090,24 @@
         <v>37.42</v>
       </c>
       <c r="L58" s="25">
-        <v>17342910.64</v>
+        <v>7844915.9</v>
       </c>
       <c r="M58" s="25">
-        <v>4335727.66</v>
+        <v>1961228.98</v>
       </c>
       <c r="N58" s="25">
-        <v>12807182.98</v>
+        <v>5683686.93</v>
       </c>
       <c r="O58" s="25">
-        <v>734202633.2</v>
+        <v>279909125.32</v>
       </c>
       <c r="P58" s="25">
-        <v>540551974.9</v>
+        <v>199831843.99</v>
       </c>
     </row>
     <row r="59" spans="2:16">
       <c r="B59" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="21">
         <v>48</v>
@@ -13109,19 +13116,19 @@
         <v>4549502</v>
       </c>
       <c r="E59" s="21">
-        <v>208518</v>
+        <v>45577</v>
       </c>
       <c r="F59" s="21">
-        <v>128978</v>
+        <v>136729</v>
       </c>
       <c r="G59" s="21">
-        <v>126700</v>
+        <v>27723</v>
       </c>
       <c r="H59" s="21">
-        <v>464196</v>
+        <v>210029</v>
       </c>
       <c r="I59" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J59" s="14">
         <v>0.75</v>
@@ -13130,24 +13137,24 @@
         <v>37.15</v>
       </c>
       <c r="L59" s="16">
-        <v>17244417.2</v>
+        <v>7802577.35</v>
       </c>
       <c r="M59" s="16">
-        <v>4311104.3</v>
+        <v>1950644.34</v>
       </c>
       <c r="N59" s="16">
-        <v>12733312.9</v>
+        <v>5651933.01</v>
       </c>
       <c r="O59" s="16">
-        <v>751447050.41</v>
+        <v>287711702.67</v>
       </c>
       <c r="P59" s="16">
-        <v>553285287.8</v>
+        <v>205483777</v>
       </c>
     </row>
     <row r="60" spans="2:16">
       <c r="B60" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C60" s="23">
         <v>49</v>
@@ -13156,19 +13163,19 @@
         <v>4557085</v>
       </c>
       <c r="E60" s="23">
-        <v>208866</v>
+        <v>45659</v>
       </c>
       <c r="F60" s="23">
-        <v>129193</v>
+        <v>136976</v>
       </c>
       <c r="G60" s="23">
-        <v>126912</v>
+        <v>27773</v>
       </c>
       <c r="H60" s="23">
-        <v>464971</v>
+        <v>210408</v>
       </c>
       <c r="I60" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J60" s="24">
         <v>0.75</v>
@@ -13177,24 +13184,24 @@
         <v>36.87</v>
       </c>
       <c r="L60" s="25">
-        <v>17145573.14</v>
+        <v>7757742.96</v>
       </c>
       <c r="M60" s="25">
-        <v>4286393.28</v>
+        <v>1939435.74</v>
       </c>
       <c r="N60" s="25">
-        <v>12659179.85</v>
+        <v>5618307.22</v>
       </c>
       <c r="O60" s="25">
-        <v>768592623.54</v>
+        <v>295469445.63</v>
       </c>
       <c r="P60" s="25">
-        <v>565944467.66</v>
+        <v>211102084.22</v>
       </c>
     </row>
     <row r="61" spans="2:16">
       <c r="B61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C61" s="21">
         <v>50</v>
@@ -13203,19 +13210,19 @@
         <v>4564680</v>
       </c>
       <c r="E61" s="21">
-        <v>209214</v>
+        <v>45740</v>
       </c>
       <c r="F61" s="21">
-        <v>129408</v>
+        <v>137219</v>
       </c>
       <c r="G61" s="21">
-        <v>127123</v>
+        <v>27823</v>
       </c>
       <c r="H61" s="21">
-        <v>465745</v>
+        <v>210782</v>
       </c>
       <c r="I61" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J61" s="14">
         <v>0.75</v>
@@ -13224,24 +13231,24 @@
         <v>36.6</v>
       </c>
       <c r="L61" s="16">
-        <v>17046267</v>
+        <v>7714621.2</v>
       </c>
       <c r="M61" s="16">
-        <v>4261566.75</v>
+        <v>1928655.3</v>
       </c>
       <c r="N61" s="16">
-        <v>12584700.25</v>
+        <v>5585965.9</v>
       </c>
       <c r="O61" s="16">
-        <v>785638890.54</v>
+        <v>303184066.83</v>
       </c>
       <c r="P61" s="16">
-        <v>578529167.91</v>
+        <v>216688050.12</v>
       </c>
     </row>
     <row r="62" spans="2:16">
       <c r="B62" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C62" s="23">
         <v>51</v>
@@ -13250,19 +13257,19 @@
         <v>4572288</v>
       </c>
       <c r="E62" s="23">
-        <v>209563</v>
+        <v>45821</v>
       </c>
       <c r="F62" s="23">
-        <v>129624</v>
+        <v>137460</v>
       </c>
       <c r="G62" s="23">
-        <v>127335</v>
+        <v>27872</v>
       </c>
       <c r="H62" s="23">
-        <v>466522</v>
+        <v>211153</v>
       </c>
       <c r="I62" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J62" s="24">
         <v>0.75</v>
@@ -13271,24 +13278,24 @@
         <v>36.6</v>
       </c>
       <c r="L62" s="25">
-        <v>17074705.2</v>
+        <v>7728199.8</v>
       </c>
       <c r="M62" s="25">
-        <v>4268676.3</v>
+        <v>1932049.95</v>
       </c>
       <c r="N62" s="25">
-        <v>12606028.9</v>
+        <v>5596149.85</v>
       </c>
       <c r="O62" s="25">
-        <v>802713595.74</v>
+        <v>310912266.63</v>
       </c>
       <c r="P62" s="25">
-        <v>591135196.8099999</v>
+        <v>222284199.97</v>
       </c>
     </row>
     <row r="63" spans="2:16">
       <c r="B63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C63" s="21">
         <v>52</v>
@@ -13297,19 +13304,19 @@
         <v>4579908</v>
       </c>
       <c r="E63" s="21">
-        <v>209912</v>
+        <v>45900</v>
       </c>
       <c r="F63" s="21">
-        <v>129840</v>
+        <v>137700</v>
       </c>
       <c r="G63" s="21">
-        <v>127547</v>
+        <v>27920</v>
       </c>
       <c r="H63" s="21">
-        <v>467299</v>
+        <v>211520</v>
       </c>
       <c r="I63" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J63" s="14">
         <v>0.75</v>
@@ -13318,24 +13325,24 @@
         <v>36.6</v>
       </c>
       <c r="L63" s="16">
-        <v>17103143.4</v>
+        <v>7741632</v>
       </c>
       <c r="M63" s="16">
-        <v>4275785.85</v>
+        <v>1935408</v>
       </c>
       <c r="N63" s="16">
-        <v>12627357.55</v>
+        <v>5606224</v>
       </c>
       <c r="O63" s="16">
-        <v>819816739.14</v>
+        <v>318653898.63</v>
       </c>
       <c r="P63" s="16">
-        <v>603762554.36</v>
+        <v>227890423.97</v>
       </c>
     </row>
     <row r="64" spans="2:16">
       <c r="B64" s="22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C64" s="23">
         <v>53</v>
@@ -13344,19 +13351,19 @@
         <v>4587541</v>
       </c>
       <c r="E64" s="23">
-        <v>210262</v>
+        <v>45980</v>
       </c>
       <c r="F64" s="23">
-        <v>130056</v>
+        <v>137938</v>
       </c>
       <c r="G64" s="23">
-        <v>127760</v>
+        <v>27968</v>
       </c>
       <c r="H64" s="23">
-        <v>468078</v>
+        <v>211886</v>
       </c>
       <c r="I64" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J64" s="24">
         <v>0.75</v>
@@ -13365,24 +13372,24 @@
         <v>36.6</v>
       </c>
       <c r="L64" s="25">
-        <v>17131654.8</v>
+        <v>7755027.6</v>
       </c>
       <c r="M64" s="25">
-        <v>4282913.7</v>
+        <v>1938756.9</v>
       </c>
       <c r="N64" s="25">
-        <v>12648741.1</v>
+        <v>5616270.7</v>
       </c>
       <c r="O64" s="25">
-        <v>836948393.9400001</v>
+        <v>326408926.23</v>
       </c>
       <c r="P64" s="25">
-        <v>616411295.46</v>
+        <v>233506694.67</v>
       </c>
     </row>
     <row r="65" spans="2:16">
       <c r="B65" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C65" s="21">
         <v>54</v>
@@ -13391,19 +13398,19 @@
         <v>4595187</v>
       </c>
       <c r="E65" s="21">
-        <v>210612</v>
+        <v>46059</v>
       </c>
       <c r="F65" s="21">
-        <v>130273</v>
+        <v>138174</v>
       </c>
       <c r="G65" s="21">
-        <v>127973</v>
+        <v>28016</v>
       </c>
       <c r="H65" s="21">
-        <v>468858</v>
+        <v>212249</v>
       </c>
       <c r="I65" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J65" s="14">
         <v>0.75</v>
@@ -13412,24 +13419,24 @@
         <v>36.6</v>
       </c>
       <c r="L65" s="16">
-        <v>17160202.8</v>
+        <v>7768313.4</v>
       </c>
       <c r="M65" s="16">
-        <v>4290050.7</v>
+        <v>1942078.35</v>
       </c>
       <c r="N65" s="16">
-        <v>12670152.1</v>
+        <v>5626235.05</v>
       </c>
       <c r="O65" s="16">
-        <v>854108596.74</v>
+        <v>334177239.63</v>
       </c>
       <c r="P65" s="16">
-        <v>629081447.5599999</v>
+        <v>239132929.72</v>
       </c>
     </row>
     <row r="66" spans="2:16">
       <c r="B66" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C66" s="23">
         <v>55</v>
@@ -13438,19 +13445,19 @@
         <v>4602846</v>
       </c>
       <c r="E66" s="23">
-        <v>210963</v>
+        <v>46137</v>
       </c>
       <c r="F66" s="23">
-        <v>130490</v>
+        <v>138411</v>
       </c>
       <c r="G66" s="23">
-        <v>128186</v>
+        <v>28064</v>
       </c>
       <c r="H66" s="23">
-        <v>469639</v>
+        <v>212612</v>
       </c>
       <c r="I66" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J66" s="24">
         <v>0.75</v>
@@ -13459,24 +13466,24 @@
         <v>36.6</v>
       </c>
       <c r="L66" s="25">
-        <v>17188787.4</v>
+        <v>7781599.2</v>
       </c>
       <c r="M66" s="25">
-        <v>4297196.85</v>
+        <v>1945399.8</v>
       </c>
       <c r="N66" s="25">
-        <v>12691590.55</v>
+        <v>5636199.4</v>
       </c>
       <c r="O66" s="25">
-        <v>871297384.14</v>
+        <v>341958838.83</v>
       </c>
       <c r="P66" s="25">
-        <v>641773038.11</v>
+        <v>244769129.12</v>
       </c>
     </row>
     <row r="67" spans="2:16">
       <c r="B67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C67" s="21">
         <v>56</v>
@@ -13485,19 +13492,19 @@
         <v>4610517</v>
       </c>
       <c r="E67" s="21">
-        <v>211315</v>
+        <v>46216</v>
       </c>
       <c r="F67" s="21">
-        <v>130708</v>
+        <v>138645</v>
       </c>
       <c r="G67" s="21">
-        <v>128400</v>
+        <v>28112</v>
       </c>
       <c r="H67" s="21">
-        <v>470423</v>
+        <v>212973</v>
       </c>
       <c r="I67" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J67" s="14">
         <v>0.75</v>
@@ -13506,24 +13513,24 @@
         <v>36.6</v>
       </c>
       <c r="L67" s="16">
-        <v>17217481.8</v>
+        <v>7794811.8</v>
       </c>
       <c r="M67" s="16">
-        <v>4304370.45</v>
+        <v>1948702.95</v>
       </c>
       <c r="N67" s="16">
-        <v>12713111.35</v>
+        <v>5646108.85</v>
       </c>
       <c r="O67" s="16">
-        <v>888514865.9400001</v>
+        <v>349753650.63</v>
       </c>
       <c r="P67" s="16">
-        <v>654486149.46</v>
+        <v>250415237.97</v>
       </c>
     </row>
     <row r="68" spans="2:16">
       <c r="B68" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C68" s="23">
         <v>57</v>
@@ -13532,19 +13539,19 @@
         <v>4618201</v>
       </c>
       <c r="E68" s="23">
-        <v>211667</v>
+        <v>46294</v>
       </c>
       <c r="F68" s="23">
-        <v>130926</v>
+        <v>138880</v>
       </c>
       <c r="G68" s="23">
-        <v>128614</v>
+        <v>28160</v>
       </c>
       <c r="H68" s="23">
-        <v>471207</v>
+        <v>213334</v>
       </c>
       <c r="I68" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J68" s="24">
         <v>0.75</v>
@@ -13553,24 +13560,24 @@
         <v>36.6</v>
       </c>
       <c r="L68" s="25">
-        <v>17246176.2</v>
+        <v>7808024.4</v>
       </c>
       <c r="M68" s="25">
-        <v>4311544.05</v>
+        <v>1952006.1</v>
       </c>
       <c r="N68" s="25">
-        <v>12734632.15</v>
+        <v>5656018.3</v>
       </c>
       <c r="O68" s="25">
-        <v>905761042.14</v>
+        <v>357561675.03</v>
       </c>
       <c r="P68" s="25">
-        <v>667220781.61</v>
+        <v>256071256.27</v>
       </c>
     </row>
     <row r="69" spans="2:16">
       <c r="B69" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C69" s="21">
         <v>58</v>
@@ -13579,19 +13586,19 @@
         <v>4625898</v>
       </c>
       <c r="E69" s="21">
-        <v>212020</v>
+        <v>46372</v>
       </c>
       <c r="F69" s="21">
-        <v>131144</v>
+        <v>139115</v>
       </c>
       <c r="G69" s="21">
-        <v>128828</v>
+        <v>28207</v>
       </c>
       <c r="H69" s="21">
-        <v>471992</v>
+        <v>213694</v>
       </c>
       <c r="I69" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J69" s="14">
         <v>0.75</v>
@@ -13600,24 +13607,24 @@
         <v>36.6</v>
       </c>
       <c r="L69" s="16">
-        <v>17274907.2</v>
+        <v>7821200.4</v>
       </c>
       <c r="M69" s="16">
-        <v>4318726.8</v>
+        <v>1955300.1</v>
       </c>
       <c r="N69" s="16">
-        <v>12756180.4</v>
+        <v>5665900.3</v>
       </c>
       <c r="O69" s="16">
-        <v>923035949.34</v>
+        <v>365382875.43</v>
       </c>
       <c r="P69" s="16">
-        <v>679976962.01</v>
+        <v>261737156.57</v>
       </c>
     </row>
     <row r="70" spans="2:16">
       <c r="B70" s="22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C70" s="23">
         <v>59</v>
@@ -13626,19 +13633,19 @@
         <v>4633608</v>
       </c>
       <c r="E70" s="23">
-        <v>212373</v>
+        <v>46450</v>
       </c>
       <c r="F70" s="23">
-        <v>131362</v>
+        <v>139350</v>
       </c>
       <c r="G70" s="23">
-        <v>129043</v>
+        <v>28255</v>
       </c>
       <c r="H70" s="23">
-        <v>472778</v>
+        <v>214055</v>
       </c>
       <c r="I70" s="24">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="J70" s="24">
         <v>0.75</v>
@@ -13647,19 +13654,19 @@
         <v>36.6</v>
       </c>
       <c r="L70" s="25">
-        <v>17303674.8</v>
+        <v>7834413</v>
       </c>
       <c r="M70" s="25">
-        <v>4325918.7</v>
+        <v>1958603.25</v>
       </c>
       <c r="N70" s="25">
-        <v>12777756.1</v>
+        <v>5675809.75</v>
       </c>
       <c r="O70" s="25">
-        <v>940339624.14</v>
+        <v>373217288.43</v>
       </c>
       <c r="P70" s="25">
-        <v>692754718.11</v>
+        <v>267412966.32</v>
       </c>
     </row>
   </sheetData>
@@ -13730,10 +13737,10 @@
         <v>1360981052.8</v>
       </c>
       <c r="D6" s="16">
-        <v>1112670380.27</v>
+        <v>1112634932.05</v>
       </c>
       <c r="E6" s="16">
-        <v>805595202.23</v>
+        <v>805586901.5899999</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -13744,10 +13751,10 @@
         <v>5895163640.9</v>
       </c>
       <c r="D7" s="16">
-        <v>7161404580.38</v>
+        <v>7161575518.4</v>
       </c>
       <c r="E7" s="16">
-        <v>8131181789.619999</v>
+        <v>8131190090.259999</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -13758,10 +13765,10 @@
         <v>-0.303047965742738</v>
       </c>
       <c r="D8" s="14">
-        <v>-0.4302067002390985</v>
+        <v>-0.4302248531068324</v>
       </c>
       <c r="E8" s="14">
-        <v>-0.5874584632703206</v>
+        <v>-0.5874627139892574</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -13813,58 +13820,58 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C15" s="16">
-        <v>61372817.22</v>
+        <v>6163030.87</v>
       </c>
       <c r="D15" s="16">
-        <v>67402845.31</v>
+        <v>10349792.95</v>
       </c>
       <c r="E15" s="16">
-        <v>60973300.41</v>
+        <v>14041808.27</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C16" s="16">
-        <v>865879707.95</v>
+        <v>228802389.89</v>
       </c>
       <c r="D16" s="16">
-        <v>940339624.1399999</v>
+        <v>373217288.4299999</v>
       </c>
       <c r="E16" s="16">
-        <v>835702365.21</v>
+        <v>496517934.55</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C17" s="16">
-        <v>636909780.9200001</v>
+        <v>159101792.41</v>
       </c>
       <c r="D17" s="16">
-        <v>692754718.11</v>
+        <v>267412966.32</v>
       </c>
       <c r="E17" s="16">
-        <v>614276773.9200001</v>
+        <v>359888450.91</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C18" s="14">
-        <v>0.0766</v>
+        <v>0.0231</v>
       </c>
       <c r="D18" s="14">
-        <v>0.102</v>
+        <v>0.0462</v>
       </c>
       <c r="E18" s="14">
-        <v>0.102</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -13872,13 +13879,13 @@
         <v>284</v>
       </c>
       <c r="C19" s="14">
-        <v>0.3782981492422077</v>
+        <v>0.64380727101137</v>
       </c>
       <c r="D19" s="14">
-        <v>0.2848367131681429</v>
+        <v>0.6438064779570211</v>
       </c>
       <c r="E19" s="14">
-        <v>0.2848367131681429</v>
+        <v>0.6438065027434741</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -13886,13 +13893,13 @@
         <v>285</v>
       </c>
       <c r="C20" s="14">
-        <v>0.2314901283588021</v>
+        <v>0.1304237230798056</v>
       </c>
       <c r="D20" s="14">
-        <v>0.2662908195218405</v>
+        <v>0.1304261179249876</v>
       </c>
       <c r="E20" s="14">
-        <v>0.2662908195218405</v>
+        <v>0.1304269884874418</v>
       </c>
     </row>
   </sheetData>
@@ -13910,7 +13917,7 @@
   <sheetPr>
     <tabColor rgb="FF7C3AED"/>
   </sheetPr>
-  <dimension ref="B2:E55"/>
+  <dimension ref="B2:E62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -14213,13 +14220,13 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="D29" s="12" t="s">
         <v>342</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>343</v>
       </c>
       <c r="E29" s="31" t="s">
         <v>291</v>
@@ -14227,7 +14234,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="4" t="s">
-        <v>128</v>
+        <v>343</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>344</v>
@@ -14255,13 +14262,13 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="D32" s="12" t="s">
         <v>350</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>351</v>
       </c>
       <c r="E32" s="31" t="s">
         <v>291</v>
@@ -14269,13 +14276,13 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C33" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="D33" s="12" t="s">
         <v>353</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>354</v>
       </c>
       <c r="E33" s="31" t="s">
         <v>291</v>
@@ -14283,237 +14290,335 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" s="31" t="s">
         <v>355</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="D34" s="12" t="s">
         <v>356</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>357</v>
       </c>
       <c r="E34" s="31" t="s">
         <v>291</v>
       </c>
     </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E35" s="31" t="s">
+        <v>291</v>
+      </c>
+    </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="B36" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E36" s="31" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="E37" s="13" t="s">
+      <c r="B37" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="E37" s="31" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E38" s="31" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="40" customHeight="1">
-      <c r="B38" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="E38" s="32" t="s">
+    <row r="43" spans="2:5" ht="40" customHeight="1">
+      <c r="B43" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E43" s="32" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="40" customHeight="1">
-      <c r="B39" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E39" s="32" t="s">
+    <row r="44" spans="2:5" ht="40" customHeight="1">
+      <c r="B44" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="E44" s="32" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="40" spans="2:5" ht="40" customHeight="1">
-      <c r="B40" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="E40" s="32" t="s">
+    <row r="45" spans="2:5" ht="40" customHeight="1">
+      <c r="B45" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="E45" s="32" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="41" spans="2:5" ht="40" customHeight="1">
-      <c r="B41" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E41" s="32" t="s">
+    <row r="46" spans="2:5" ht="40" customHeight="1">
+      <c r="B46" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="E46" s="32" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="2:5" ht="40" customHeight="1">
-      <c r="B42" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="E42" s="32" t="s">
+    <row r="47" spans="2:5" ht="40" customHeight="1">
+      <c r="B47" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="E47" s="32" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="E45" s="13" t="s">
+    <row r="48" spans="2:5" ht="40" customHeight="1">
+      <c r="B48" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E48" s="32" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="40" customHeight="1">
+      <c r="B49" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="E49" s="32" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="B51" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="B52" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="2:5">
-      <c r="B46" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="E46" s="33" t="s">
+    <row r="53" spans="2:5">
+      <c r="B53" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E53" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>385</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="E47" s="33" t="s">
+    <row r="54" spans="2:5">
+      <c r="B54" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E54" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="48" spans="2:5">
-      <c r="B48" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C48" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E48" s="33" t="s">
+    <row r="55" spans="2:5">
+      <c r="B55" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="E55" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="E49" s="33" t="s">
+    <row r="56" spans="2:5">
+      <c r="B56" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E56" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="C50" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="E50" s="33" t="s">
+    <row r="57" spans="2:5">
+      <c r="B57" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>411</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="E57" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="E51" s="33" t="s">
+    <row r="58" spans="2:5">
+      <c r="B58" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E58" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="52" spans="2:5">
-      <c r="B52" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>400</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="E52" s="33" t="s">
+    <row r="59" spans="2:5">
+      <c r="B59" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="E59" s="33" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="2:5">
-      <c r="B55" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
+    <row r="62" spans="2:5">
+      <c r="B62" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -14521,9 +14626,9 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B62:E62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
